--- a/plugins/fs-analysis/skills/analyzing-financial-statements/assets/template.xlsx
+++ b/plugins/fs-analysis/skills/analyzing-financial-statements/assets/template.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr codeName="Questa_cartella_di_lavoro"/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="600" windowWidth="29040" windowHeight="15720" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Input" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Report" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Input" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Report" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'Report'!$A$1:$D$185</definedName>
@@ -1378,7 +1378,7 @@
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <plotArea>
       <layout/>
@@ -1388,7 +1388,7 @@
           <idx val="0"/>
           <order val="0"/>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -1396,10 +1396,10 @@
             <idx val="0"/>
             <bubble3D val="0"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="00B050"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="19050">
+              <a:ln w="19050">
                 <a:solidFill>
                   <a:schemeClr val="lt1"/>
                 </a:solidFill>
@@ -1411,13 +1411,13 @@
             <idx val="1"/>
             <bubble3D val="0"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:schemeClr val="tx2">
                   <a:lumMod val="40000"/>
                   <a:lumOff val="60000"/>
                 </a:schemeClr>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="19050">
+              <a:ln w="19050">
                 <a:solidFill>
                   <a:schemeClr val="lt1"/>
                 </a:solidFill>
@@ -1429,8 +1429,8 @@
             <idx val="2"/>
             <bubble3D val="0"/>
             <spPr>
-              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="19050">
+              <a:noFill/>
+              <a:ln w="19050">
                 <a:solidFill>
                   <a:schemeClr val="lt1"/>
                 </a:solidFill>
@@ -1474,8 +1474,8 @@
     <dispBlanksAs val="gap"/>
   </chart>
   <spPr>
-    <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
+    <a:noFill/>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
       <a:noFill/>
       <a:prstDash val="solid"/>
       <a:round/>
@@ -1485,7 +1485,7 @@
 </file>
 
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <plotArea>
       <layout/>
@@ -1495,7 +1495,7 @@
           <idx val="0"/>
           <order val="0"/>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -1503,12 +1503,12 @@
             <idx val="0"/>
             <bubble3D val="0"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:schemeClr val="accent3">
                   <a:lumMod val="75000"/>
                 </a:schemeClr>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="19050">
+              <a:ln w="19050">
                 <a:solidFill>
                   <a:schemeClr val="lt1"/>
                 </a:solidFill>
@@ -1520,13 +1520,13 @@
             <idx val="1"/>
             <bubble3D val="0"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:schemeClr val="tx2">
                   <a:lumMod val="40000"/>
                   <a:lumOff val="60000"/>
                 </a:schemeClr>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="19050">
+              <a:ln w="19050">
                 <a:solidFill>
                   <a:schemeClr val="lt1"/>
                 </a:solidFill>
@@ -1538,8 +1538,8 @@
             <idx val="2"/>
             <bubble3D val="0"/>
             <spPr>
-              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="19050">
+              <a:noFill/>
+              <a:ln w="19050">
                 <a:solidFill>
                   <a:schemeClr val="lt1"/>
                 </a:solidFill>
@@ -1583,8 +1583,8 @@
     <dispBlanksAs val="gap"/>
   </chart>
   <spPr>
-    <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
+    <a:noFill/>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
       <a:noFill/>
       <a:prstDash val="solid"/>
       <a:round/>
@@ -1594,7 +1594,7 @@
 </file>
 
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <plotArea>
       <layout/>
@@ -1604,7 +1604,7 @@
           <idx val="0"/>
           <order val="0"/>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -1612,12 +1612,12 @@
             <idx val="0"/>
             <bubble3D val="0"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:schemeClr val="accent4">
                   <a:lumMod val="75000"/>
                 </a:schemeClr>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="19050">
+              <a:ln w="19050">
                 <a:solidFill>
                   <a:schemeClr val="lt1"/>
                 </a:solidFill>
@@ -1629,13 +1629,13 @@
             <idx val="1"/>
             <bubble3D val="0"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:schemeClr val="tx2">
                   <a:lumMod val="40000"/>
                   <a:lumOff val="60000"/>
                 </a:schemeClr>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="19050">
+              <a:ln w="19050">
                 <a:solidFill>
                   <a:schemeClr val="lt1"/>
                 </a:solidFill>
@@ -1647,8 +1647,8 @@
             <idx val="2"/>
             <bubble3D val="0"/>
             <spPr>
-              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="19050">
+              <a:noFill/>
+              <a:ln w="19050">
                 <a:solidFill>
                   <a:schemeClr val="lt1"/>
                 </a:solidFill>
@@ -1692,8 +1692,8 @@
     <dispBlanksAs val="gap"/>
   </chart>
   <spPr>
-    <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
+    <a:noFill/>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
       <a:noFill/>
       <a:prstDash val="solid"/>
       <a:round/>
@@ -1703,7 +1703,7 @@
 </file>
 
 <file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <plotArea>
       <layout/>
@@ -1713,7 +1713,7 @@
           <idx val="0"/>
           <order val="0"/>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -1721,10 +1721,10 @@
             <idx val="0"/>
             <bubble3D val="0"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:schemeClr val="accent1"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="19050">
+              <a:ln w="19050">
                 <a:solidFill>
                   <a:schemeClr val="lt1"/>
                 </a:solidFill>
@@ -1736,10 +1736,10 @@
             <idx val="1"/>
             <bubble3D val="0"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:schemeClr val="tx1"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="19050">
+              <a:ln w="19050">
                 <a:solidFill>
                   <a:schemeClr val="lt1"/>
                 </a:solidFill>
@@ -1751,8 +1751,8 @@
             <idx val="2"/>
             <bubble3D val="0"/>
             <spPr>
-              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="19050">
+              <a:noFill/>
+              <a:ln w="19050">
                 <a:solidFill>
                   <a:schemeClr val="lt1"/>
                 </a:solidFill>
@@ -1796,8 +1796,8 @@
     <dispBlanksAs val="gap"/>
   </chart>
   <spPr>
-    <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
+    <a:noFill/>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
       <a:noFill/>
       <a:prstDash val="solid"/>
       <a:round/>
@@ -1807,7 +1807,7 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <twoCellAnchor>
     <from>
       <col>2</col>
@@ -1827,9 +1827,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+          <c:chart r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -1854,9 +1854,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+          <c:chart r:id="rId2"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -1881,9 +1881,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+          <c:chart r:id="rId3"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -1908,9 +1908,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
+          <c:chart r:id="rId4"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -1933,26 +1933,26 @@
       <nvPicPr>
         <cNvPr id="18" name="Immagine 17"/>
         <cNvPicPr>
-          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1" noChangeArrowheads="1"/>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId5"/>
-        <a:srcRect xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:blip cstate="print" r:embed="rId5"/>
+        <a:srcRect/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr bwMode="auto">
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:xfrm>
           <a:off x="7479031" y="92003"/>
           <a:ext cx="485425" cy="288997"/>
         </a:xfrm>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
+        <a:prstGeom prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:noFill/>
+        <a:ln>
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -1976,26 +1976,26 @@
       <nvPicPr>
         <cNvPr id="21" name="Immagine 20"/>
         <cNvPicPr>
-          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1" noChangeArrowheads="1"/>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId6"/>
-        <a:srcRect xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:blip cstate="print" r:embed="rId6"/>
+        <a:srcRect/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr bwMode="auto">
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:xfrm>
           <a:off x="7541420" y="12741117"/>
           <a:ext cx="433992" cy="271937"/>
         </a:xfrm>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
+        <a:prstGeom prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:noFill/>
+        <a:ln>
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -2019,26 +2019,26 @@
       <nvPicPr>
         <cNvPr id="3" name="Immagine 2"/>
         <cNvPicPr>
-          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1" noChangeArrowheads="1"/>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId7"/>
-        <a:srcRect xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:blip cstate="print" r:embed="rId7"/>
+        <a:srcRect/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr bwMode="auto">
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:xfrm>
           <a:off x="7570470" y="38593395"/>
           <a:ext cx="414942" cy="275747"/>
         </a:xfrm>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
+        <a:prstGeom prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:noFill/>
+        <a:ln>
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -4232,7 +4232,7 @@
         <v/>
       </c>
       <c r="D83" s="54">
-        <f>_xlfn.XLOOKUP(C83,$G$95:$G$104,$H$95:$H$104)*_xlfn.XLOOKUP(I92,$G$84:$G$87,$K$84:$K$87)</f>
+        <f>INDEX($H$95:$H$104,MATCH(C83,$G$95:$G$104,0))*INDEX($K$84:$K$87,MATCH(I92,$G$84:$G$87,0))</f>
         <v/>
       </c>
       <c r="E83" s="2" t="n"/>
@@ -4441,15 +4441,15 @@
       <c r="F89" s="2" t="n"/>
       <c r="G89" s="2" t="n"/>
       <c r="H89" s="28">
-        <f t="array" ref="H89">_xlfn.IFS(H88&lt;=H84,$G$84,AND(H88&lt;=H85,H88&gt;H84),$G$85,AND(H88&lt;=H86,H88&gt;H85),$G$86,H88&gt;H86,$G$87)</f>
+        <f>IF(H88&lt;=H84,$G$84,IF(AND(H88&lt;=H85,H88&gt;H84),$G$85,IF(AND(H88&lt;=H86,H88&gt;H85),$G$86,IF(H88&gt;H86,$G$87))))</f>
         <v/>
       </c>
       <c r="I89" s="28">
-        <f t="array" ref="I89">_xlfn.IFS(I88&lt;=I84,$G$84,AND(I88&lt;=I85,I88&gt;I84),$G$85,AND(I88&lt;=I86,I88&gt;I85),$G$86,I88&gt;I86,$G$87)</f>
+        <f>IF(I88&lt;=I84,$G$84,IF(AND(I88&lt;=I85,I88&gt;I84),$G$85,IF(AND(I88&lt;=I86,I88&gt;I85),$G$86,IF(I88&gt;I86,$G$87))))</f>
         <v/>
       </c>
       <c r="J89" s="28">
-        <f t="array" ref="J89">_xlfn.IFS(J88&lt;=J84,$G$84,AND(J88&lt;=J85,J88&gt;J84),$G$85,AND(J88&lt;=J86,J88&gt;J85),$G$86,J88&gt;J86,$G$87)</f>
+        <f>IF(J88&lt;=J84,$G$84,IF(AND(J88&lt;=J85,J88&gt;J84),$G$85,IF(AND(J88&lt;=J86,J88&gt;J85),$G$86,IF(J88&gt;J86,$G$87))))</f>
         <v/>
       </c>
       <c r="K89" s="2" t="n"/>
@@ -4469,15 +4469,15 @@
       <c r="F90" s="2" t="n"/>
       <c r="G90" s="2" t="n"/>
       <c r="H90" s="27">
-        <f>_xlfn.XLOOKUP(H89,$G$84:$G$87,$F$84:$F$87)</f>
+        <f>INDEX($F$84:$F$87,MATCH(H89,$G$84:$G$87,0))</f>
         <v/>
       </c>
       <c r="I90" s="27">
-        <f>_xlfn.XLOOKUP(I89,$G$84:$G$87,$F$84:$F$87)</f>
+        <f>INDEX($F$84:$F$87,MATCH(I89,$G$84:$G$87,0))</f>
         <v/>
       </c>
       <c r="J90" s="27">
-        <f>_xlfn.XLOOKUP(J89,$G$84:$G$87,$F$84:$F$87)</f>
+        <f>INDEX($F$84:$F$87,MATCH(J89,$G$84:$G$87,0))</f>
         <v/>
       </c>
       <c r="K90" s="2" t="n"/>
@@ -4520,7 +4520,7 @@
       <c r="G92" s="2" t="n"/>
       <c r="H92" s="2" t="n"/>
       <c r="I92" s="50">
-        <f>IFERROR(_xlfn.XLOOKUP(I91,$F$84:$F$87,G84:G87),_xlfn.XLOOKUP(MEDIAN(H90:J90),$F$84:$F$87,$G$84:$G$87))</f>
+        <f>IFERROR(INDEX(G84:G87,MATCH(I91,$F$84:$F$87,0)),INDEX($G$84:$G$87,MATCH(MEDIAN(H90:J90),$F$84:$F$87,0)))</f>
         <v/>
       </c>
       <c r="J92" s="2" t="n"/>
@@ -5770,7 +5770,7 @@
         <v/>
       </c>
       <c r="B14" s="87">
-        <f>_xlfn.XLOOKUP(Input!C135,Input!D119:H119,Input!D118:H118)</f>
+        <f>INDEX(Input.$D$118:$H$118,MATCH(Input!C135,Input.$D$119:$H$119,0))</f>
         <v/>
       </c>
       <c r="D14" s="14" t="n"/>

--- a/plugins/fs-analysis/skills/analyzing-financial-statements/assets/template.xlsx
+++ b/plugins/fs-analysis/skills/analyzing-financial-statements/assets/template.xlsx
@@ -18,24 +18,23 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="15">
+  <numFmts count="14">
     <numFmt numFmtId="164" formatCode="0.000"/>
     <numFmt numFmtId="165" formatCode="0.0"/>
     <numFmt numFmtId="166" formatCode="0.0000"/>
     <numFmt numFmtId="167" formatCode="#,##0.00\ &quot;€&quot;"/>
-    <numFmt numFmtId="168" formatCode="#,##0.00\ &quot;€&quot;;\-#,##0.00\ &quot;€&quot;"/>
-    <numFmt numFmtId="169" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="170" formatCode="#,##0.00\ _€;\-#,##0.00\ _€"/>
-    <numFmt numFmtId="171" formatCode="[$-410]0"/>
-    <numFmt numFmtId="172" formatCode="[$-410]#,##0.00"/>
-    <numFmt numFmtId="173" formatCode="[$-410]#,##0.00\ &quot;€&quot;;[$-410]\-#,##0.00\ &quot;€&quot;"/>
-    <numFmt numFmtId="174" formatCode="[$-410]#,##0.00\ &quot;€&quot;"/>
-    <numFmt numFmtId="175" formatCode="[$-410]#,##0"/>
-    <numFmt numFmtId="176" formatCode="[$-410]0.00%"/>
-    <numFmt numFmtId="177" formatCode="[$-410]0%"/>
-    <numFmt numFmtId="178" formatCode="[$-410]0.00"/>
+    <numFmt numFmtId="168" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="169" formatCode="#,##0.00\ _€;\-#,##0.00\ _€"/>
+    <numFmt numFmtId="170" formatCode="[$-410]0"/>
+    <numFmt numFmtId="171" formatCode="[$-410]#,##0.00"/>
+    <numFmt numFmtId="172" formatCode="[$-410]#,##0.00\ &quot;€&quot;;[$-410]\-#,##0.00\ &quot;€&quot;"/>
+    <numFmt numFmtId="173" formatCode="[$-410]#,##0.00\ &quot;€&quot;"/>
+    <numFmt numFmtId="174" formatCode="[$-410]#,##0"/>
+    <numFmt numFmtId="175" formatCode="[$-410]0.00%"/>
+    <numFmt numFmtId="176" formatCode="[$-410]0%"/>
+    <numFmt numFmtId="177" formatCode="[$-410]0.00"/>
   </numFmts>
-  <fonts count="36">
+  <fonts count="37">
     <font>
       <name val="Arial"/>
       <family val="2"/>
@@ -252,6 +251,12 @@
       <b val="1"/>
       <color theme="1"/>
       <sz val="28"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="11"/>
     </font>
   </fonts>
   <fills count="15">
@@ -768,7 +773,7 @@
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="227">
+  <cellXfs count="225">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -910,7 +915,6 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="1" fontId="15" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -918,22 +922,13 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="21" fillId="3" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="10" fontId="22" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="10" fontId="24" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="2"/>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="10" fontId="24" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="2"/>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="21" fillId="3" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="10" fontId="22" fillId="3" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="21" fillId="3" borderId="9" pivotButton="0" quotePrefix="1" xfId="0"/>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="10" fontId="24" fillId="0" borderId="13" pivotButton="0" quotePrefix="0" xfId="2"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="23" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="24" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -941,31 +936,14 @@
     <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="9" fontId="24" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="2"/>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="24" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="2"/>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="10" fontId="22" fillId="3" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="21" fillId="3" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="10" fontId="22" fillId="3" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="20" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="2" fontId="11" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="11" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="11" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="11" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="17" fillId="11" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -989,9 +967,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="centerContinuous"/>
-    </xf>
-    <xf numFmtId="1" fontId="12" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="centerContinuous"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1004,25 +979,16 @@
     <xf numFmtId="0" fontId="29" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="30" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="28" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="30" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="30" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="9" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="169" fontId="17" fillId="12" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="168" fontId="17" fillId="12" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
     <xf numFmtId="0" fontId="17" fillId="13" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="21" fillId="14" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="18" fillId="14" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="26" fillId="12" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="17" fillId="12" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="18" fillId="14" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1032,28 +998,7 @@
     <xf numFmtId="0" fontId="15" fillId="12" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="11" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="11" fillId="0" borderId="22" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="17" fillId="11" borderId="35" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="11" fillId="0" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="11" fillId="0" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="11" fillId="0" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="11" fillId="0" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="11" fillId="0" borderId="33" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="11" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1067,37 +1012,14 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="12" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="2" fontId="11" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="11" fillId="0" borderId="22" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="31" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="11" fillId="0" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="11" fillId="3" borderId="3" pivotButton="0" quotePrefix="0" xfId="1"/>
-    <xf numFmtId="3" fontId="18" fillId="3" borderId="3" pivotButton="0" quotePrefix="0" xfId="1"/>
-    <xf numFmtId="3" fontId="11" fillId="3" borderId="5" pivotButton="0" quotePrefix="0" xfId="1"/>
-    <xf numFmtId="3" fontId="18" fillId="3" borderId="6" pivotButton="0" quotePrefix="0" xfId="1"/>
-    <xf numFmtId="3" fontId="11" fillId="3" borderId="4" pivotButton="0" quotePrefix="0" xfId="1"/>
-    <xf numFmtId="1" fontId="35" fillId="0" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="17" fillId="12" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="4" fontId="18" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="34" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -1105,57 +1027,167 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="170" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="169" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
     <xf numFmtId="4" fontId="3" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="12" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="centerContinuous"/>
+    </xf>
+    <xf numFmtId="170" fontId="15" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="171" fontId="18" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="35" fillId="0" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="172" fontId="30" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="173" fontId="30" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="174" fontId="11" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="175" fontId="22" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="175" fontId="24" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="175" fontId="24" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="174" fontId="18" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="174" fontId="11" fillId="3" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="175" fontId="22" fillId="3" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="175" fontId="24" fillId="0" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="24" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="24" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="174" fontId="11" fillId="3" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="175" fontId="22" fillId="3" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="174" fontId="18" fillId="3" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="175" fontId="22" fillId="3" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="175" fontId="11" fillId="0" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="11" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="11" fillId="0" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="11" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="174" fontId="11" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="174" fontId="11" fillId="0" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="175" fontId="11" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="175" fontId="11" fillId="0" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="11" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="11" fillId="0" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="11" fillId="0" borderId="22" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="11" fillId="0" borderId="33" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="11" fillId="0" borderId="22" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="justify" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="27" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="170" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
-    <xf numFmtId="171" fontId="12" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="170" fontId="12" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="centerContinuous"/>
     </xf>
-    <xf numFmtId="171" fontId="15" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="172" fontId="18" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="171" fontId="35" fillId="0" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="173" fontId="30" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="174" fontId="30" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="justify" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="169" fontId="17" fillId="12" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
-    <xf numFmtId="175" fontId="11" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="22" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+    <xf numFmtId="170" fontId="15" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="171" fontId="18" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="35" fillId="0" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="172" fontId="30" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="173" fontId="30" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="17" fillId="12" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="174" fontId="11" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="175" fontId="22" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="175" fontId="24" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="175" fontId="24" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="174" fontId="18" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="174" fontId="11" fillId="3" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="175" fontId="22" fillId="3" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="175" fontId="24" fillId="0" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="24" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
@@ -1164,77 +1196,62 @@
     <xf numFmtId="176" fontId="24" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="175" fontId="18" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="175" fontId="11" fillId="3" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="22" fillId="3" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="24" fillId="0" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="24" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="24" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="175" fontId="11" fillId="3" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="22" fillId="3" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="175" fontId="18" fillId="3" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="22" fillId="3" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="11" fillId="0" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="11" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="11" fillId="0" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="11" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="174" fontId="11" fillId="3" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="175" fontId="22" fillId="3" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="174" fontId="18" fillId="3" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="175" fontId="22" fillId="3" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="175" fontId="11" fillId="0" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="11" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="11" fillId="0" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="11" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="175" fontId="11" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="175" fontId="11" fillId="0" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="11" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="11" fillId="0" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="171" fontId="11" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="171" fontId="11" fillId="0" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="171" fontId="11" fillId="0" borderId="22" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="171" fontId="11" fillId="0" borderId="33" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="11" fillId="0" borderId="22" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="174" fontId="11" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="174" fontId="11" fillId="0" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="175" fontId="11" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="175" fontId="11" fillId="0" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="11" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="11" fillId="0" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="11" fillId="0" borderId="22" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="11" fillId="0" borderId="33" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="11" fillId="0" borderId="22" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="22" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -1243,7 +1260,7 @@
     <cellStyle name="Percentuale" xfId="2" builtinId="5"/>
     <cellStyle name="Valuta" xfId="3" builtinId="4"/>
   </cellStyles>
-  <dxfs count="37">
+  <dxfs count="38">
     <dxf>
       <font>
         <color rgb="FFFF0000"/>
@@ -1457,6 +1474,11 @@
           <bgColor rgb="FFFF0000"/>
         </patternFill>
       </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFFC000"/>
+      </font>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -2472,62 +2494,62 @@
   <dimension ref="A1:Q143"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.875" defaultRowHeight="14.25"/>
   <cols>
-    <col width="50.5" customWidth="1" min="1" max="1"/>
-    <col width="15.375" customWidth="1" min="2" max="2"/>
-    <col width="14.125" customWidth="1" min="3" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18.375" customWidth="1" min="6" max="6"/>
-    <col width="12.625" customWidth="1" min="7" max="7"/>
-    <col width="18.125" customWidth="1" min="8" max="8"/>
-    <col width="13.5" customWidth="1" min="9" max="9"/>
-    <col width="11.625" customWidth="1" min="10" max="10"/>
-    <col width="11.5" customWidth="1" min="12" max="12"/>
-    <col width="14.625" customWidth="1" min="13" max="13"/>
-    <col width="15" customWidth="1" min="16" max="16"/>
-    <col width="25.875" customWidth="1" min="17" max="17"/>
-    <col width="44.5" customWidth="1" min="18" max="18"/>
-    <col width="27.625" bestFit="1" customWidth="1" min="19" max="19"/>
+    <col width="50.5" customWidth="1" style="183" min="1" max="1"/>
+    <col width="15.375" customWidth="1" style="183" min="2" max="2"/>
+    <col width="14.125" customWidth="1" style="183" min="3" max="4"/>
+    <col width="18" customWidth="1" style="183" min="5" max="5"/>
+    <col width="18.375" customWidth="1" style="183" min="6" max="6"/>
+    <col width="12.625" customWidth="1" style="183" min="7" max="7"/>
+    <col width="18.125" customWidth="1" style="183" min="8" max="8"/>
+    <col width="13.5" customWidth="1" style="183" min="9" max="9"/>
+    <col width="11.625" customWidth="1" style="183" min="10" max="10"/>
+    <col width="11.5" customWidth="1" style="183" min="12" max="12"/>
+    <col width="14.625" customWidth="1" style="183" min="13" max="13"/>
+    <col width="15" customWidth="1" style="183" min="16" max="16"/>
+    <col width="25.875" customWidth="1" style="183" min="17" max="17"/>
+    <col width="44.5" customWidth="1" style="183" min="18" max="18"/>
+    <col width="27.625" bestFit="1" customWidth="1" style="183" min="19" max="19"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" customHeight="1">
+    <row r="1" ht="15" customHeight="1" s="183">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Inserire Nome Azienda</t>
         </is>
       </c>
       <c r="B1" s="9" t="n"/>
-      <c r="C1" s="162" t="inlineStr">
+      <c r="C1" s="136" t="inlineStr">
         <is>
           <t>Tipologia</t>
         </is>
       </c>
-      <c r="D1" s="162" t="inlineStr">
+      <c r="D1" s="136" t="inlineStr">
         <is>
           <t>Grade</t>
         </is>
       </c>
-      <c r="E1" s="162" t="inlineStr">
+      <c r="E1" s="136" t="inlineStr">
         <is>
           <t>Fido</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="15" customHeight="1">
+    <row r="2" ht="15" customHeight="1" s="183">
       <c r="A2" s="1" t="inlineStr">
         <is>
           <t>Inserire ultimo anno disponibile di bilancio</t>
         </is>
       </c>
       <c r="B2" s="9" t="n"/>
-      <c r="C2" s="129" t="inlineStr">
+      <c r="C2" s="115" t="inlineStr">
         <is>
           <t>Fornitore</t>
         </is>
       </c>
-      <c r="D2" s="129" t="n"/>
-      <c r="E2" s="189" t="n"/>
-    </row>
-    <row r="4" ht="15" customHeight="1">
+      <c r="D2" s="115" t="n"/>
+      <c r="E2" s="188" t="n"/>
+    </row>
+    <row r="4" ht="15" customHeight="1" s="183">
       <c r="A4" s="1" t="inlineStr">
         <is>
           <t>CONTO ECONOMICO</t>
@@ -2538,14 +2560,14 @@
       <c r="D4" s="2" t="n"/>
       <c r="E4" s="2" t="n"/>
     </row>
-    <row r="5" ht="15" customHeight="1">
+    <row r="5" ht="15" customHeight="1" s="183">
       <c r="A5" s="2" t="n"/>
       <c r="B5" s="2" t="n"/>
       <c r="C5" s="2" t="n"/>
       <c r="D5" s="2" t="n"/>
       <c r="E5" s="2" t="n"/>
     </row>
-    <row r="6" ht="15.75" customHeight="1">
+    <row r="6" ht="15.75" customHeight="1" s="183">
       <c r="A6" s="3" t="inlineStr">
         <is>
           <t>Voce</t>
@@ -2565,7 +2587,7 @@
       </c>
       <c r="E6" s="2" t="n"/>
     </row>
-    <row r="7" ht="15" customHeight="1">
+    <row r="7" ht="15" customHeight="1" s="183">
       <c r="A7" s="2" t="inlineStr">
         <is>
           <t>Valore della Produzione</t>
@@ -2580,7 +2602,7 @@
       <c r="D7" s="4" t="n"/>
       <c r="E7" s="2" t="n"/>
     </row>
-    <row r="8" ht="15" customHeight="1">
+    <row r="8" ht="15" customHeight="1" s="183">
       <c r="A8" s="2" t="inlineStr">
         <is>
           <t>Ricavi di vendita</t>
@@ -2595,7 +2617,7 @@
       <c r="D8" s="4" t="n"/>
       <c r="E8" s="2" t="n"/>
     </row>
-    <row r="9" ht="15" customHeight="1">
+    <row r="9" ht="15" customHeight="1" s="183">
       <c r="A9" s="2" t="inlineStr">
         <is>
           <t>Costi della Produzione</t>
@@ -2610,7 +2632,7 @@
       <c r="D9" s="4" t="n"/>
       <c r="E9" s="2" t="n"/>
     </row>
-    <row r="10" ht="15" customHeight="1">
+    <row r="10" ht="15" customHeight="1" s="183">
       <c r="A10" s="2" t="inlineStr">
         <is>
           <t>Costi per Materie</t>
@@ -2625,7 +2647,7 @@
       <c r="D10" s="4" t="n"/>
       <c r="E10" s="2" t="n"/>
     </row>
-    <row r="11" ht="15" customHeight="1">
+    <row r="11" ht="15" customHeight="1" s="183">
       <c r="A11" s="2" t="inlineStr">
         <is>
           <t>Costi per Servizi</t>
@@ -2640,7 +2662,7 @@
       <c r="D11" s="4" t="n"/>
       <c r="E11" s="2" t="n"/>
     </row>
-    <row r="12" ht="15" customHeight="1">
+    <row r="12" ht="15" customHeight="1" s="183">
       <c r="A12" s="2" t="inlineStr">
         <is>
           <t>Costi per godimento beni di terzi</t>
@@ -2655,7 +2677,7 @@
       <c r="D12" s="4" t="n"/>
       <c r="E12" s="2" t="n"/>
     </row>
-    <row r="13" ht="15" customHeight="1">
+    <row r="13" ht="15" customHeight="1" s="183">
       <c r="A13" s="2" t="inlineStr">
         <is>
           <t>Costi Personale</t>
@@ -2670,7 +2692,7 @@
       <c r="D13" s="4" t="n"/>
       <c r="E13" s="2" t="n"/>
     </row>
-    <row r="14" ht="15" customHeight="1">
+    <row r="14" ht="15" customHeight="1" s="183">
       <c r="A14" s="2" t="inlineStr">
         <is>
           <t>Ammortamenti</t>
@@ -2687,7 +2709,7 @@
       <c r="F14" s="70" t="n"/>
       <c r="G14" s="11" t="n"/>
     </row>
-    <row r="15" ht="15" customHeight="1">
+    <row r="15" ht="15" customHeight="1" s="183">
       <c r="A15" s="2" t="inlineStr">
         <is>
           <t>Accantonamenti per rischi</t>
@@ -2702,7 +2724,7 @@
       <c r="D15" s="4" t="n"/>
       <c r="E15" s="2" t="n"/>
     </row>
-    <row r="16" ht="15" customHeight="1">
+    <row r="16" ht="15" customHeight="1" s="183">
       <c r="A16" s="2" t="inlineStr">
         <is>
           <t>Oneri diversi di gestione</t>
@@ -2717,7 +2739,7 @@
       <c r="D16" s="4" t="n"/>
       <c r="E16" s="2" t="n"/>
     </row>
-    <row r="17" ht="15" customHeight="1">
+    <row r="17" ht="15" customHeight="1" s="183">
       <c r="A17" s="2" t="inlineStr">
         <is>
           <t>EBIT</t>
@@ -2732,7 +2754,7 @@
       <c r="D17" s="4" t="n"/>
       <c r="E17" s="2" t="n"/>
     </row>
-    <row r="18" ht="15" customHeight="1">
+    <row r="18" ht="15" customHeight="1" s="183">
       <c r="A18" s="2" t="inlineStr">
         <is>
           <t>Proventi Finanziari</t>
@@ -2747,7 +2769,7 @@
       <c r="D18" s="4" t="n"/>
       <c r="E18" s="2" t="n"/>
     </row>
-    <row r="19" ht="15" customHeight="1">
+    <row r="19" ht="15" customHeight="1" s="183">
       <c r="A19" s="2" t="inlineStr">
         <is>
           <t>Oneri Finanziari</t>
@@ -2762,7 +2784,7 @@
       <c r="D19" s="4" t="n"/>
       <c r="E19" s="2" t="n"/>
     </row>
-    <row r="20" ht="15" customHeight="1">
+    <row r="20" ht="15" customHeight="1" s="183">
       <c r="A20" s="2" t="inlineStr">
         <is>
           <t>Utile (Perdita) dell'esercizio</t>
@@ -2777,7 +2799,7 @@
       <c r="D20" s="4" t="n"/>
       <c r="E20" s="2" t="n"/>
     </row>
-    <row r="21" ht="15" customHeight="1">
+    <row r="21" ht="15" customHeight="1" s="183">
       <c r="A21" s="2" t="inlineStr">
         <is>
           <t>Dipendenti</t>
@@ -2799,14 +2821,14 @@
       <c r="D22" s="5" t="n"/>
       <c r="E22" s="5" t="n"/>
     </row>
-    <row r="23" ht="15" customHeight="1">
+    <row r="23" ht="15" customHeight="1" s="183">
       <c r="A23" s="2" t="n"/>
       <c r="B23" s="2" t="n"/>
       <c r="C23" s="2" t="n"/>
       <c r="D23" s="2" t="n"/>
       <c r="E23" s="2" t="n"/>
     </row>
-    <row r="24" ht="15" customHeight="1">
+    <row r="24" ht="15" customHeight="1" s="183">
       <c r="A24" s="1" t="inlineStr">
         <is>
           <t>STATO PATRIMONIALE</t>
@@ -2817,14 +2839,14 @@
       <c r="D24" s="2" t="n"/>
       <c r="E24" s="2" t="n"/>
     </row>
-    <row r="25" ht="15" customHeight="1">
+    <row r="25" ht="15" customHeight="1" s="183">
       <c r="A25" s="2" t="n"/>
       <c r="B25" s="2" t="n"/>
       <c r="C25" s="2" t="n"/>
       <c r="D25" s="2" t="n"/>
       <c r="E25" s="2" t="n"/>
     </row>
-    <row r="26" ht="15" customHeight="1">
+    <row r="26" ht="15" customHeight="1" s="183">
       <c r="A26" s="3" t="inlineStr">
         <is>
           <t>Voce</t>
@@ -2844,7 +2866,7 @@
       </c>
       <c r="E26" s="2" t="n"/>
     </row>
-    <row r="27" ht="15" customHeight="1">
+    <row r="27" ht="15" customHeight="1" s="183">
       <c r="A27" s="2" t="inlineStr">
         <is>
           <t>Immobilizzazioni</t>
@@ -2859,7 +2881,7 @@
       <c r="D27" s="4" t="n"/>
       <c r="E27" s="2" t="n"/>
     </row>
-    <row r="28" ht="15" customHeight="1">
+    <row r="28" ht="15" customHeight="1" s="183">
       <c r="A28" s="2" t="inlineStr">
         <is>
           <t>Rimanenze</t>
@@ -2876,7 +2898,7 @@
       <c r="F28" s="11" t="n"/>
       <c r="G28" s="11" t="n"/>
     </row>
-    <row r="29" ht="15" customHeight="1">
+    <row r="29" ht="15" customHeight="1" s="183">
       <c r="A29" s="2" t="inlineStr">
         <is>
           <t>Crediti</t>
@@ -2891,7 +2913,7 @@
       <c r="D29" s="4" t="n"/>
       <c r="E29" s="2" t="n"/>
     </row>
-    <row r="30" ht="15" customHeight="1">
+    <row r="30" ht="15" customHeight="1" s="183">
       <c r="A30" s="2" t="inlineStr">
         <is>
           <t>Attività Finanziarie</t>
@@ -2906,7 +2928,7 @@
       <c r="D30" s="4" t="n"/>
       <c r="E30" s="2" t="n"/>
     </row>
-    <row r="31" ht="15" customHeight="1">
+    <row r="31" ht="15" customHeight="1" s="183">
       <c r="A31" s="2" t="inlineStr">
         <is>
           <t>Disponibilità Liquide</t>
@@ -2922,7 +2944,7 @@
       <c r="E31" s="2" t="n"/>
       <c r="F31" s="11" t="n"/>
     </row>
-    <row r="32" ht="15" customHeight="1">
+    <row r="32" ht="15" customHeight="1" s="183">
       <c r="A32" s="2" t="inlineStr">
         <is>
           <t>Ratei e Risconti Attivi</t>
@@ -2938,7 +2960,7 @@
       <c r="E32" s="2" t="n"/>
       <c r="F32" s="11" t="n"/>
     </row>
-    <row r="33" ht="15" customHeight="1">
+    <row r="33" ht="15" customHeight="1" s="183">
       <c r="A33" s="2" t="inlineStr">
         <is>
           <t>Totale Attivo</t>
@@ -2954,7 +2976,7 @@
       <c r="E33" s="2" t="n"/>
       <c r="F33" s="11" t="n"/>
     </row>
-    <row r="34" ht="15" customHeight="1">
+    <row r="34" ht="15" customHeight="1" s="183">
       <c r="A34" s="2" t="inlineStr">
         <is>
           <t>Totale Patrimonio Netto</t>
@@ -2970,7 +2992,7 @@
       <c r="E34" s="2" t="n"/>
       <c r="F34" s="11" t="n"/>
     </row>
-    <row r="35" ht="15" customHeight="1">
+    <row r="35" ht="15" customHeight="1" s="183">
       <c r="A35" s="2" t="inlineStr">
         <is>
           <t>Fondi per rischi e oneri</t>
@@ -2987,7 +3009,7 @@
       <c r="F35" s="11" t="n"/>
       <c r="H35" s="11" t="n"/>
     </row>
-    <row r="36" ht="15" customHeight="1">
+    <row r="36" ht="15" customHeight="1" s="183">
       <c r="A36" s="2" t="inlineStr">
         <is>
           <t>Trattamento di fine rapporto di lavoro subordinato</t>
@@ -3006,7 +3028,7 @@
       <c r="I36" s="11" t="n"/>
       <c r="J36" s="11" t="n"/>
     </row>
-    <row r="37" ht="15" customHeight="1">
+    <row r="37" ht="15" customHeight="1" s="183">
       <c r="A37" s="2" t="inlineStr">
         <is>
           <t>Totale Debiti</t>
@@ -3019,21 +3041,21 @@
         <v>0</v>
       </c>
       <c r="D37" s="4" t="n"/>
-      <c r="E37" s="179">
+      <c r="E37" s="144">
         <f>E38+E39</f>
         <v/>
       </c>
-      <c r="F37" s="179">
+      <c r="F37" s="144">
         <f>F38+F39</f>
         <v/>
       </c>
-      <c r="G37" s="179">
+      <c r="G37" s="144">
         <f>G38+G39</f>
         <v/>
       </c>
       <c r="H37" s="11" t="n"/>
     </row>
-    <row r="38" ht="15" customHeight="1">
+    <row r="38" ht="15" customHeight="1" s="183">
       <c r="A38" s="2" t="inlineStr">
         <is>
           <t>Debiti esigibili a breve</t>
@@ -3046,20 +3068,20 @@
         <v>0</v>
       </c>
       <c r="D38" s="4" t="n"/>
-      <c r="E38" s="179">
+      <c r="E38" s="144">
         <f>B38-B41</f>
         <v/>
       </c>
-      <c r="F38" s="179">
+      <c r="F38" s="144">
         <f>C38-C41</f>
         <v/>
       </c>
-      <c r="G38" s="179">
+      <c r="G38" s="144">
         <f>D38-D41</f>
         <v/>
       </c>
     </row>
-    <row r="39" ht="15" customHeight="1">
+    <row r="39" ht="15" customHeight="1" s="183">
       <c r="A39" s="2" t="inlineStr">
         <is>
           <t>Debiti esigibili oltre l’esercizio successivo</t>
@@ -3072,20 +3094,20 @@
         <v>0</v>
       </c>
       <c r="D39" s="16" t="n"/>
-      <c r="E39" s="179">
+      <c r="E39" s="144">
         <f>B39-B42</f>
         <v/>
       </c>
-      <c r="F39" s="179">
+      <c r="F39" s="144">
         <f>C39-C42</f>
         <v/>
       </c>
-      <c r="G39" s="179">
+      <c r="G39" s="144">
         <f>D39-D42</f>
         <v/>
       </c>
     </row>
-    <row r="40" ht="15" customHeight="1">
+    <row r="40" ht="15" customHeight="1" s="183">
       <c r="A40" s="2" t="inlineStr">
         <is>
           <t>Totale Debiti Finanziari</t>
@@ -3100,7 +3122,7 @@
       <c r="D40" s="4" t="n"/>
       <c r="E40" s="2" t="n"/>
     </row>
-    <row r="41" ht="15" customHeight="1">
+    <row r="41" ht="15" customHeight="1" s="183">
       <c r="A41" s="2" t="inlineStr">
         <is>
           <t>Debiti Finanziari esigibili a breve</t>
@@ -3115,7 +3137,7 @@
       <c r="D41" s="4" t="n"/>
       <c r="E41" s="2" t="n"/>
     </row>
-    <row r="42" ht="15" customHeight="1">
+    <row r="42" ht="15" customHeight="1" s="183">
       <c r="A42" s="2" t="inlineStr">
         <is>
           <t>Debiti Finanziari esigibili oltre l’esercizio successivo</t>
@@ -3130,7 +3152,7 @@
       <c r="D42" s="4" t="n"/>
       <c r="E42" s="2" t="n"/>
     </row>
-    <row r="43" ht="15" customHeight="1">
+    <row r="43" ht="15" customHeight="1" s="183">
       <c r="A43" s="2" t="inlineStr">
         <is>
           <t>Ratei e Risconti Passivi</t>
@@ -3145,7 +3167,7 @@
       <c r="D43" s="4" t="n"/>
       <c r="E43" s="2" t="n"/>
     </row>
-    <row r="44" ht="15" customHeight="1">
+    <row r="44" ht="15" customHeight="1" s="183">
       <c r="A44" s="2" t="inlineStr">
         <is>
           <t>Debiti verso fornitori</t>
@@ -3160,7 +3182,7 @@
       <c r="D44" s="4" t="n"/>
       <c r="E44" s="2" t="n"/>
     </row>
-    <row r="45" ht="15" customHeight="1">
+    <row r="45" ht="15" customHeight="1" s="183">
       <c r="A45" s="2" t="inlineStr">
         <is>
           <t>Crediti verso clienti</t>
@@ -3175,7 +3197,7 @@
       <c r="D45" s="4" t="n"/>
       <c r="E45" s="2" t="n"/>
     </row>
-    <row r="46" ht="15" customHeight="1">
+    <row r="46" ht="15" customHeight="1" s="183">
       <c r="A46" s="2" t="inlineStr">
         <is>
           <t>ATECO 2007</t>
@@ -3185,7 +3207,7 @@
       <c r="C46" s="9" t="n"/>
       <c r="D46" s="9" t="n"/>
     </row>
-    <row r="47" ht="15" customHeight="1">
+    <row r="47" ht="15" customHeight="1" s="183">
       <c r="A47" s="2" t="inlineStr">
         <is>
           <t>Partita IVA</t>
@@ -3194,12 +3216,12 @@
       <c r="B47" s="9" t="n"/>
       <c r="C47" s="9" t="n"/>
       <c r="D47" s="9" t="n"/>
-      <c r="E47" s="180">
+      <c r="E47" s="145">
         <f>IF(LEN(B47)=10,"0"&amp;B47,IF(LEN(B47)=9,"00"&amp;B47,B47))</f>
         <v/>
       </c>
     </row>
-    <row r="48" ht="15" customHeight="1">
+    <row r="48" ht="15" customHeight="1" s="183">
       <c r="A48" s="2" t="inlineStr">
         <is>
           <t>Forma Giuridica</t>
@@ -3209,7 +3231,7 @@
       <c r="C48" s="9" t="n"/>
       <c r="D48" s="9" t="n"/>
     </row>
-    <row r="49" ht="15" customHeight="1">
+    <row r="49" ht="15" customHeight="1" s="183">
       <c r="A49" s="2" t="inlineStr">
         <is>
           <t>Sede</t>
@@ -3219,7 +3241,7 @@
       <c r="C49" s="9" t="n"/>
       <c r="D49" s="9" t="n"/>
     </row>
-    <row r="52" ht="15" customHeight="1">
+    <row r="52" ht="15" customHeight="1" s="183">
       <c r="A52" s="2" t="inlineStr">
         <is>
           <t>Verifica Attivo</t>
@@ -3239,7 +3261,7 @@
       </c>
       <c r="F52" s="63" t="n"/>
     </row>
-    <row r="53" ht="15" customHeight="1">
+    <row r="53" ht="15" customHeight="1" s="183">
       <c r="A53" s="2" t="inlineStr">
         <is>
           <t>Verifica Passivo</t>
@@ -3259,8 +3281,8 @@
       </c>
       <c r="F53" s="63" t="n"/>
     </row>
-    <row r="54" ht="15" customHeight="1" thickBot="1"/>
-    <row r="55" ht="15.95" customHeight="1" thickBot="1">
+    <row r="54" ht="15" customHeight="1" s="183" thickBot="1"/>
+    <row r="55" ht="15.95" customHeight="1" s="183" thickBot="1">
       <c r="A55" s="2" t="n"/>
       <c r="B55" s="2" t="n"/>
       <c r="C55" s="2" t="n"/>
@@ -3268,22 +3290,22 @@
       <c r="E55" s="2" t="n"/>
       <c r="F55" s="2" t="n"/>
       <c r="G55" s="2" t="n"/>
-      <c r="H55" s="181" t="inlineStr">
+      <c r="H55" s="184" t="inlineStr">
         <is>
           <t>Grade</t>
         </is>
       </c>
-      <c r="I55" s="182" t="n"/>
-      <c r="J55" s="182" t="n"/>
-      <c r="K55" s="182" t="n"/>
-      <c r="L55" s="182" t="n"/>
-      <c r="M55" s="182" t="n"/>
-      <c r="N55" s="182" t="n"/>
-      <c r="O55" s="182" t="n"/>
-      <c r="P55" s="182" t="n"/>
-      <c r="Q55" s="183" t="n"/>
-    </row>
-    <row r="56" ht="15" customHeight="1">
+      <c r="I55" s="185" t="n"/>
+      <c r="J55" s="185" t="n"/>
+      <c r="K55" s="185" t="n"/>
+      <c r="L55" s="185" t="n"/>
+      <c r="M55" s="185" t="n"/>
+      <c r="N55" s="185" t="n"/>
+      <c r="O55" s="185" t="n"/>
+      <c r="P55" s="185" t="n"/>
+      <c r="Q55" s="186" t="n"/>
+    </row>
+    <row r="56" ht="15" customHeight="1" s="183">
       <c r="A56" s="20" t="inlineStr">
         <is>
           <t>Liquidità</t>
@@ -3346,7 +3368,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="57" ht="15" customHeight="1">
+    <row r="57" ht="15" customHeight="1" s="183">
       <c r="A57" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Test Acido </t>
@@ -3405,7 +3427,7 @@
         </is>
       </c>
     </row>
-    <row r="58" ht="15" customHeight="1">
+    <row r="58" ht="15" customHeight="1" s="183">
       <c r="A58" s="2" t="inlineStr">
         <is>
           <t>Current Ratio</t>
@@ -3464,7 +3486,7 @@
         </is>
       </c>
     </row>
-    <row r="59" ht="15" customHeight="1">
+    <row r="59" ht="15" customHeight="1" s="183">
       <c r="A59" s="20" t="inlineStr">
         <is>
           <t>Indebitamento e sostenibilità del debito</t>
@@ -3487,7 +3509,7 @@
       <c r="P59" s="30" t="n"/>
       <c r="Q59" s="30" t="n"/>
     </row>
-    <row r="60" ht="15" customHeight="1">
+    <row r="60" ht="15" customHeight="1" s="183">
       <c r="A60" s="2" t="inlineStr">
         <is>
           <t>Rapporto Indebitamento</t>
@@ -3546,7 +3568,7 @@
         </is>
       </c>
     </row>
-    <row r="61" ht="15" customHeight="1">
+    <row r="61" ht="15" customHeight="1" s="183">
       <c r="A61" s="2" t="inlineStr">
         <is>
           <t>PFN/EBITDA</t>
@@ -3605,7 +3627,7 @@
         </is>
       </c>
     </row>
-    <row r="62" ht="15" customHeight="1">
+    <row r="62" ht="15" customHeight="1" s="183">
       <c r="A62" s="2" t="inlineStr">
         <is>
           <t>IMS</t>
@@ -3664,7 +3686,7 @@
         </is>
       </c>
     </row>
-    <row r="63" ht="15" customHeight="1">
+    <row r="63" ht="15" customHeight="1" s="183">
       <c r="A63" s="2" t="inlineStr">
         <is>
           <t>Interest Coverage Ratio</t>
@@ -3723,7 +3745,7 @@
         </is>
       </c>
     </row>
-    <row r="64" ht="15" customHeight="1">
+    <row r="64" ht="15" customHeight="1" s="183">
       <c r="A64" s="20" t="inlineStr">
         <is>
           <t>Redditività</t>
@@ -3746,7 +3768,7 @@
       <c r="P64" s="30" t="n"/>
       <c r="Q64" s="30" t="n"/>
     </row>
-    <row r="65" ht="15" customHeight="1">
+    <row r="65" ht="15" customHeight="1" s="183">
       <c r="A65" s="2" t="inlineStr">
         <is>
           <t>ROS</t>
@@ -3805,7 +3827,7 @@
         </is>
       </c>
     </row>
-    <row r="66" ht="15" customHeight="1">
+    <row r="66" ht="15" customHeight="1" s="183">
       <c r="A66" s="2" t="inlineStr">
         <is>
           <t>ROE</t>
@@ -3864,7 +3886,7 @@
         </is>
       </c>
     </row>
-    <row r="67" ht="15" customHeight="1">
+    <row r="67" ht="15" customHeight="1" s="183">
       <c r="A67" s="2" t="inlineStr">
         <is>
           <t>ROI</t>
@@ -3923,7 +3945,7 @@
         </is>
       </c>
     </row>
-    <row r="68" ht="15" customHeight="1">
+    <row r="68" ht="15" customHeight="1" s="183">
       <c r="A68" s="2" t="inlineStr">
         <is>
           <t>EBITDA%</t>
@@ -3982,7 +4004,7 @@
         </is>
       </c>
     </row>
-    <row r="69" ht="15" customHeight="1">
+    <row r="69" ht="15" customHeight="1" s="183">
       <c r="A69" s="2" t="inlineStr">
         <is>
           <t>EBIT%</t>
@@ -4041,7 +4063,7 @@
         </is>
       </c>
     </row>
-    <row r="70" ht="15" customHeight="1">
+    <row r="70" ht="15" customHeight="1" s="183">
       <c r="A70" s="2" t="inlineStr">
         <is>
           <t>Risultato d'esercizio%</t>
@@ -4100,7 +4122,7 @@
         </is>
       </c>
     </row>
-    <row r="71" ht="15" customHeight="1">
+    <row r="71" ht="15" customHeight="1" s="183">
       <c r="A71" s="20" t="inlineStr">
         <is>
           <t>Efficienza</t>
@@ -4123,7 +4145,7 @@
       <c r="P71" s="21" t="n"/>
       <c r="Q71" s="21" t="n"/>
     </row>
-    <row r="72" ht="15" customHeight="1">
+    <row r="72" ht="15" customHeight="1" s="183">
       <c r="A72" s="2" t="inlineStr">
         <is>
           <t>Asset Turnover (AT)</t>
@@ -4182,7 +4204,7 @@
         </is>
       </c>
     </row>
-    <row r="73" ht="15.95" customHeight="1" thickBot="1">
+    <row r="73" ht="15.95" customHeight="1" s="183" thickBot="1">
       <c r="A73" s="2" t="n"/>
       <c r="B73" s="2" t="n"/>
       <c r="C73" s="2" t="n"/>
@@ -4201,12 +4223,12 @@
       <c r="P73" s="2" t="n"/>
       <c r="Q73" s="2" t="n"/>
     </row>
-    <row r="74" ht="15.95" customHeight="1" thickBot="1">
+    <row r="74" ht="15.95" customHeight="1" s="183" thickBot="1">
       <c r="A74" s="2" t="n"/>
       <c r="B74" s="2" t="n"/>
       <c r="C74" s="2" t="n"/>
       <c r="D74" s="2" t="n"/>
-      <c r="E74" s="181" t="inlineStr">
+      <c r="E74" s="184" t="inlineStr">
         <is>
           <t>Grade</t>
         </is>
@@ -4224,7 +4246,7 @@
       <c r="P74" s="2" t="n"/>
       <c r="Q74" s="2" t="n"/>
     </row>
-    <row r="75" ht="15.95" customHeight="1" thickBot="1">
+    <row r="75" ht="15.95" customHeight="1" s="183" thickBot="1">
       <c r="A75" s="2" t="n"/>
       <c r="B75" s="2" t="n"/>
       <c r="C75" s="2" t="n"/>
@@ -4237,7 +4259,7 @@
       <c r="G75" s="2" t="n"/>
       <c r="Q75" s="2" t="n"/>
     </row>
-    <row r="76" ht="15" customHeight="1">
+    <row r="76" ht="15" customHeight="1" s="183">
       <c r="A76" s="2" t="n"/>
       <c r="B76" s="2" t="n"/>
       <c r="C76" s="2" t="n"/>
@@ -4256,7 +4278,7 @@
       <c r="P76" s="2" t="n"/>
       <c r="Q76" s="2" t="n"/>
     </row>
-    <row r="77" ht="15" customHeight="1">
+    <row r="77" ht="15" customHeight="1" s="183">
       <c r="A77" s="2" t="n"/>
       <c r="B77" s="2" t="n"/>
       <c r="C77" s="2" t="n"/>
@@ -4275,7 +4297,7 @@
       <c r="P77" s="2" t="n"/>
       <c r="Q77" s="2" t="n"/>
     </row>
-    <row r="78" ht="15" customHeight="1">
+    <row r="78" ht="15" customHeight="1" s="183">
       <c r="A78" s="2" t="n"/>
       <c r="B78" s="2" t="n"/>
       <c r="C78" s="2" t="n"/>
@@ -4294,7 +4316,7 @@
       <c r="P78" s="2" t="n"/>
       <c r="Q78" s="2" t="n"/>
     </row>
-    <row r="79" ht="15" customHeight="1">
+    <row r="79" ht="15" customHeight="1" s="183">
       <c r="A79" s="2" t="n"/>
       <c r="B79" s="2" t="n"/>
       <c r="C79" s="2" t="n"/>
@@ -4313,7 +4335,7 @@
       <c r="P79" s="2" t="n"/>
       <c r="Q79" s="2" t="n"/>
     </row>
-    <row r="80" ht="15.95" customHeight="1" thickBot="1">
+    <row r="80" ht="15.95" customHeight="1" s="183" thickBot="1">
       <c r="A80" s="2" t="n"/>
       <c r="B80" s="2" t="n"/>
       <c r="C80" s="2" t="n"/>
@@ -4332,7 +4354,7 @@
       <c r="P80" s="2" t="n"/>
       <c r="Q80" s="2" t="n"/>
     </row>
-    <row r="81" ht="15.95" customHeight="1" thickBot="1">
+    <row r="81" ht="15.95" customHeight="1" s="183" thickBot="1">
       <c r="A81" s="2" t="n"/>
       <c r="B81" s="45" t="n"/>
       <c r="C81" s="46" t="n"/>
@@ -4351,7 +4373,7 @@
       <c r="P81" s="2" t="n"/>
       <c r="Q81" s="2" t="n"/>
     </row>
-    <row r="82" ht="15.95" customHeight="1" thickBot="1">
+    <row r="82" ht="15.95" customHeight="1" s="183" thickBot="1">
       <c r="A82" s="2" t="n"/>
       <c r="B82" s="48" t="n"/>
       <c r="C82" s="49" t="inlineStr">
@@ -4378,7 +4400,7 @@
       <c r="P82" s="2" t="n"/>
       <c r="Q82" s="2" t="n"/>
     </row>
-    <row r="83" ht="15.95" customHeight="1" thickBot="1">
+    <row r="83" ht="15.95" customHeight="1" s="183" thickBot="1">
       <c r="A83" s="1" t="n"/>
       <c r="B83" s="51" t="n"/>
       <c r="C83" s="52">
@@ -4423,7 +4445,7 @@
       <c r="P83" s="2" t="n"/>
       <c r="Q83" s="2" t="n"/>
     </row>
-    <row r="84" ht="15.95" customHeight="1" thickBot="1">
+    <row r="84" ht="15.95" customHeight="1" s="183" thickBot="1">
       <c r="A84" s="2" t="n"/>
       <c r="B84" s="51" t="n"/>
       <c r="C84" s="2" t="n"/>
@@ -4456,12 +4478,12 @@
       <c r="P84" s="2" t="n"/>
       <c r="Q84" s="2" t="n"/>
     </row>
-    <row r="85" ht="15.95" customHeight="1" thickBot="1">
+    <row r="85" ht="15.95" customHeight="1" s="183" thickBot="1">
       <c r="A85" s="2" t="n"/>
       <c r="B85" s="51" t="n"/>
       <c r="C85" s="2" t="n"/>
       <c r="D85" s="55">
-        <f>"0 € - "&amp;TEXT(D83,"#.##0")&amp;" €"</f>
+        <f>"0 € - "&amp;TEXT(D83,"[$-410]#,##0")&amp;" €"</f>
         <v/>
       </c>
       <c r="E85" s="2" t="n"/>
@@ -4492,7 +4514,7 @@
       <c r="P85" s="2" t="n"/>
       <c r="Q85" s="2" t="n"/>
     </row>
-    <row r="86" ht="15" customHeight="1">
+    <row r="86" ht="15" customHeight="1" s="183">
       <c r="A86" s="2" t="n"/>
       <c r="B86" s="51" t="n"/>
       <c r="C86" s="2" t="n"/>
@@ -4525,7 +4547,7 @@
       <c r="P86" s="2" t="n"/>
       <c r="Q86" s="2" t="n"/>
     </row>
-    <row r="87" ht="15" customHeight="1">
+    <row r="87" ht="15" customHeight="1" s="183">
       <c r="A87" s="2" t="n"/>
       <c r="B87" s="51" t="n"/>
       <c r="C87" s="2" t="n"/>
@@ -4558,7 +4580,7 @@
       <c r="P87" s="2" t="n"/>
       <c r="Q87" s="2" t="n"/>
     </row>
-    <row r="88" ht="15" customHeight="1">
+    <row r="88" ht="15" customHeight="1" s="183">
       <c r="A88" s="1" t="n"/>
       <c r="B88" s="56" t="n"/>
       <c r="C88" s="19" t="n"/>
@@ -4586,7 +4608,7 @@
       <c r="P88" s="2" t="n"/>
       <c r="Q88" s="2" t="n"/>
     </row>
-    <row r="89" ht="15" customHeight="1">
+    <row r="89" ht="15" customHeight="1" s="183">
       <c r="A89" s="2" t="n"/>
       <c r="B89" s="56" t="n"/>
       <c r="C89" s="19" t="n"/>
@@ -4614,7 +4636,7 @@
       <c r="P89" s="2" t="n"/>
       <c r="Q89" s="2" t="n"/>
     </row>
-    <row r="90" ht="15" customHeight="1">
+    <row r="90" ht="15" customHeight="1" s="183">
       <c r="A90" s="2" t="n"/>
       <c r="B90" s="56" t="n"/>
       <c r="C90" s="19" t="n"/>
@@ -4642,7 +4664,7 @@
       <c r="P90" s="2" t="n"/>
       <c r="Q90" s="2" t="n"/>
     </row>
-    <row r="91" ht="15.95" customHeight="1" thickBot="1">
+    <row r="91" ht="15.95" customHeight="1" s="183" thickBot="1">
       <c r="A91" s="2" t="n"/>
       <c r="B91" s="56" t="n"/>
       <c r="C91" s="19" t="n"/>
@@ -4664,7 +4686,7 @@
       <c r="P91" s="2" t="n"/>
       <c r="Q91" s="2" t="n"/>
     </row>
-    <row r="92" ht="15.95" customHeight="1" thickBot="1">
+    <row r="92" ht="15.95" customHeight="1" s="183" thickBot="1">
       <c r="A92" s="2" t="n"/>
       <c r="B92" s="51" t="n"/>
       <c r="C92" s="2" t="n"/>
@@ -4686,7 +4708,7 @@
       <c r="P92" s="2" t="n"/>
       <c r="Q92" s="2" t="n"/>
     </row>
-    <row r="93" ht="15.95" customHeight="1" thickBot="1">
+    <row r="93" ht="15.95" customHeight="1" s="183" thickBot="1">
       <c r="A93" s="2" t="n"/>
       <c r="B93" s="51" t="n"/>
       <c r="C93" s="2" t="n"/>
@@ -4705,7 +4727,7 @@
       <c r="P93" s="2" t="n"/>
       <c r="Q93" s="2" t="n"/>
     </row>
-    <row r="94" ht="15.95" customHeight="1" thickBot="1">
+    <row r="94" ht="15.95" customHeight="1" s="183" thickBot="1">
       <c r="A94" s="2" t="n"/>
       <c r="B94" s="51" t="n"/>
       <c r="C94" s="2" t="n"/>
@@ -4732,7 +4754,7 @@
       <c r="P94" s="2" t="n"/>
       <c r="Q94" s="2" t="n"/>
     </row>
-    <row r="95" ht="15.95" customHeight="1" thickBot="1">
+    <row r="95" ht="15.95" customHeight="1" s="183" thickBot="1">
       <c r="A95" s="1" t="n"/>
       <c r="B95" s="51" t="n"/>
       <c r="C95" s="2" t="n"/>
@@ -4755,7 +4777,7 @@
       <c r="P95" s="2" t="n"/>
       <c r="Q95" s="2" t="n"/>
     </row>
-    <row r="96" ht="15.95" customHeight="1" thickBot="1">
+    <row r="96" ht="15.95" customHeight="1" s="183" thickBot="1">
       <c r="A96" s="2" t="n"/>
       <c r="B96" s="51" t="n"/>
       <c r="C96" s="2" t="n"/>
@@ -4778,7 +4800,7 @@
       <c r="P96" s="2" t="n"/>
       <c r="Q96" s="2" t="n"/>
     </row>
-    <row r="97" ht="15.95" customHeight="1" thickBot="1">
+    <row r="97" ht="15.95" customHeight="1" s="183" thickBot="1">
       <c r="A97" s="2" t="n"/>
       <c r="B97" s="51" t="n"/>
       <c r="C97" s="2" t="n"/>
@@ -4801,7 +4823,7 @@
       <c r="P97" s="2" t="n"/>
       <c r="Q97" s="2" t="n"/>
     </row>
-    <row r="98" ht="15.95" customHeight="1" thickBot="1">
+    <row r="98" ht="15.95" customHeight="1" s="183" thickBot="1">
       <c r="A98" s="2" t="n"/>
       <c r="B98" s="51" t="n"/>
       <c r="C98" s="2" t="n"/>
@@ -4824,7 +4846,7 @@
       <c r="P98" s="2" t="n"/>
       <c r="Q98" s="2" t="n"/>
     </row>
-    <row r="99" ht="15.95" customHeight="1" thickBot="1">
+    <row r="99" ht="15.95" customHeight="1" s="183" thickBot="1">
       <c r="A99" s="2" t="n"/>
       <c r="B99" s="51" t="n"/>
       <c r="C99" s="2" t="n"/>
@@ -4847,7 +4869,7 @@
       <c r="P99" s="2" t="n"/>
       <c r="Q99" s="2" t="n"/>
     </row>
-    <row r="100" ht="15.95" customHeight="1" thickBot="1">
+    <row r="100" ht="15.95" customHeight="1" s="183" thickBot="1">
       <c r="A100" s="2" t="n"/>
       <c r="B100" s="51" t="n"/>
       <c r="C100" s="2" t="n"/>
@@ -4870,7 +4892,7 @@
       <c r="P100" s="2" t="n"/>
       <c r="Q100" s="2" t="n"/>
     </row>
-    <row r="101" ht="15.95" customHeight="1" thickBot="1">
+    <row r="101" ht="15.95" customHeight="1" s="183" thickBot="1">
       <c r="A101" s="2" t="n"/>
       <c r="B101" s="51" t="n"/>
       <c r="C101" s="2" t="n"/>
@@ -4893,7 +4915,7 @@
       <c r="P101" s="2" t="n"/>
       <c r="Q101" s="2" t="n"/>
     </row>
-    <row r="102" ht="15.95" customHeight="1" thickBot="1">
+    <row r="102" ht="15.95" customHeight="1" s="183" thickBot="1">
       <c r="A102" s="2" t="n"/>
       <c r="B102" s="51" t="n"/>
       <c r="C102" s="2" t="n"/>
@@ -4916,7 +4938,7 @@
       <c r="P102" s="2" t="n"/>
       <c r="Q102" s="2" t="n"/>
     </row>
-    <row r="103" ht="15.95" customHeight="1" thickBot="1">
+    <row r="103" ht="15.95" customHeight="1" s="183" thickBot="1">
       <c r="A103" s="2" t="n"/>
       <c r="B103" s="51" t="n"/>
       <c r="C103" s="2" t="n"/>
@@ -4939,7 +4961,7 @@
       <c r="P103" s="2" t="n"/>
       <c r="Q103" s="2" t="n"/>
     </row>
-    <row r="104" ht="15.95" customHeight="1" thickBot="1">
+    <row r="104" ht="15.95" customHeight="1" s="183" thickBot="1">
       <c r="A104" s="2" t="n"/>
       <c r="B104" s="51" t="n"/>
       <c r="C104" s="2" t="n"/>
@@ -4962,7 +4984,7 @@
       <c r="P104" s="2" t="n"/>
       <c r="Q104" s="2" t="n"/>
     </row>
-    <row r="105" ht="15.95" customHeight="1" thickBot="1">
+    <row r="105" ht="15.95" customHeight="1" s="183" thickBot="1">
       <c r="A105" s="2" t="n"/>
       <c r="B105" s="60" t="n"/>
       <c r="C105" s="5" t="n"/>
@@ -4982,12 +5004,12 @@
       <c r="Q105" s="2" t="n"/>
     </row>
     <row r="109">
-      <c r="B109" s="127">
+      <c r="B109" s="113">
         <f>$C$83</f>
         <v/>
       </c>
     </row>
-    <row r="110" ht="15" customHeight="1">
+    <row r="110" ht="15" customHeight="1" s="183">
       <c r="A110" s="24" t="inlineStr">
         <is>
           <t>Grafico</t>
@@ -5003,7 +5025,7 @@
           <t>Rosso</t>
         </is>
       </c>
-      <c r="D110" s="180" t="inlineStr">
+      <c r="D110" s="145" t="inlineStr">
         <is>
           <t>Giallo</t>
         </is>
@@ -5015,7 +5037,7 @@
       </c>
       <c r="F110" s="2" t="n"/>
     </row>
-    <row r="111" ht="15" customHeight="1">
+    <row r="111" ht="15" customHeight="1" s="183">
       <c r="A111" s="2" t="n"/>
       <c r="B111" s="67">
         <f>$C$83</f>
@@ -5035,7 +5057,7 @@
       </c>
       <c r="F111" s="2" t="n"/>
     </row>
-    <row r="112" ht="15" customHeight="1">
+    <row r="112" ht="15" customHeight="1" s="183">
       <c r="A112" s="2" t="n"/>
       <c r="B112" s="67">
         <f>10-B113</f>
@@ -5055,7 +5077,7 @@
       </c>
       <c r="F112" s="2" t="n"/>
     </row>
-    <row r="113" ht="15" customHeight="1">
+    <row r="113" ht="15" customHeight="1" s="183">
       <c r="A113" s="2" t="n"/>
       <c r="B113" s="67">
         <f>IF(B111=10,B111,"")</f>
@@ -5075,7 +5097,7 @@
       </c>
       <c r="F113" s="2" t="n"/>
     </row>
-    <row r="114" ht="15" customHeight="1">
+    <row r="114" ht="15" customHeight="1" s="183">
       <c r="A114" s="2" t="n"/>
       <c r="B114" s="67" t="n">
         <v>10</v>
@@ -5091,7 +5113,7 @@
       </c>
       <c r="F114" s="2" t="n"/>
     </row>
-    <row r="115" ht="15" customHeight="1">
+    <row r="115" ht="15" customHeight="1" s="183">
       <c r="A115" s="2" t="n"/>
       <c r="B115" s="2" t="n"/>
       <c r="C115" s="2" t="n"/>
@@ -5099,7 +5121,7 @@
       <c r="E115" s="2" t="n"/>
       <c r="F115" s="2" t="n"/>
     </row>
-    <row r="116" ht="15" customHeight="1">
+    <row r="116" ht="15" customHeight="1" s="183">
       <c r="A116" s="2" t="n"/>
       <c r="B116" s="2" t="n"/>
       <c r="C116" s="2" t="n"/>
@@ -5107,14 +5129,14 @@
       <c r="E116" s="2" t="n"/>
       <c r="F116" s="2" t="n"/>
     </row>
-    <row r="117" ht="15" customHeight="1">
+    <row r="117" ht="15" customHeight="1" s="183">
       <c r="B117" s="2" t="n"/>
       <c r="C117" s="2" t="n"/>
       <c r="D117" s="2" t="n"/>
       <c r="E117" s="2" t="n"/>
       <c r="F117" s="2" t="n"/>
     </row>
-    <row r="118" ht="15" customHeight="1">
+    <row r="118" ht="15" customHeight="1" s="183">
       <c r="A118" s="2" t="n"/>
       <c r="B118" s="1" t="inlineStr">
         <is>
@@ -5136,7 +5158,7 @@
           <t>Critica</t>
         </is>
       </c>
-      <c r="F118" s="187" t="inlineStr">
+      <c r="F118" s="146" t="inlineStr">
         <is>
           <t>Adeguata</t>
         </is>
@@ -5152,7 +5174,7 @@
         </is>
       </c>
     </row>
-    <row r="119" ht="15" customHeight="1">
+    <row r="119" ht="15" customHeight="1" s="183">
       <c r="A119" s="2" t="n"/>
       <c r="B119" s="2" t="n"/>
       <c r="C119" s="2" t="n"/>
@@ -5162,7 +5184,7 @@
       <c r="E119" s="74" t="n">
         <v>4</v>
       </c>
-      <c r="F119" s="188" t="n">
+      <c r="F119" s="147" t="n">
         <v>3</v>
       </c>
       <c r="G119" s="75" t="n">
@@ -5172,7 +5194,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="120" ht="15" customHeight="1">
+    <row r="120" ht="15" customHeight="1" s="183">
       <c r="A120" s="72" t="inlineStr">
         <is>
           <t>Reddituale</t>
@@ -5186,7 +5208,7 @@
       <c r="G120" s="72" t="n"/>
       <c r="H120" s="72" t="n"/>
     </row>
-    <row r="121" ht="15" customHeight="1">
+    <row r="121" ht="15" customHeight="1" s="183">
       <c r="A121" s="2" t="inlineStr">
         <is>
           <t>Crescita Fatturato</t>
@@ -5216,7 +5238,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="122" ht="15" customHeight="1">
+    <row r="122" ht="15" customHeight="1" s="183">
       <c r="A122" s="2" t="inlineStr">
         <is>
           <t>Crescita EBIT</t>
@@ -5246,7 +5268,7 @@
         <v>0.07000000000000001</v>
       </c>
     </row>
-    <row r="123" ht="15" customHeight="1">
+    <row r="123" ht="15" customHeight="1" s="183">
       <c r="A123" s="2" t="inlineStr">
         <is>
           <t>Crescita Peso EBIT</t>
@@ -5276,7 +5298,7 @@
         <v>0.07000000000000001</v>
       </c>
     </row>
-    <row r="124" ht="15" customHeight="1">
+    <row r="124" ht="15" customHeight="1" s="183">
       <c r="A124" s="2" t="inlineStr">
         <is>
           <t>Crescita Utile</t>
@@ -5306,7 +5328,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="125" ht="15" customHeight="1">
+    <row r="125" ht="15" customHeight="1" s="183">
       <c r="A125" s="2" t="inlineStr">
         <is>
           <t>Crescita Peso Utile</t>
@@ -5336,7 +5358,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="126" ht="15" customHeight="1">
+    <row r="126" ht="15" customHeight="1" s="183">
       <c r="A126" s="2" t="inlineStr">
         <is>
           <t>ROS</t>
@@ -5366,7 +5388,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="127" ht="15" customHeight="1">
+    <row r="127" ht="15" customHeight="1" s="183">
       <c r="A127" s="72" t="inlineStr">
         <is>
           <t>Media</t>
@@ -5383,7 +5405,7 @@
       <c r="G127" s="2" t="n"/>
       <c r="H127" s="2" t="n"/>
     </row>
-    <row r="128" ht="15" customHeight="1">
+    <row r="128" ht="15" customHeight="1" s="183">
       <c r="A128" s="2" t="n"/>
       <c r="B128" s="2" t="n"/>
       <c r="C128" s="2" t="n"/>
@@ -5393,7 +5415,7 @@
       <c r="G128" s="2" t="n"/>
       <c r="H128" s="2" t="n"/>
     </row>
-    <row r="129" ht="15" customHeight="1">
+    <row r="129" ht="15" customHeight="1" s="183">
       <c r="A129" s="72" t="inlineStr">
         <is>
           <t>Finanziaria</t>
@@ -5407,7 +5429,7 @@
       <c r="G129" s="72" t="n"/>
       <c r="H129" s="72" t="n"/>
     </row>
-    <row r="130" ht="15" customHeight="1">
+    <row r="130" ht="15" customHeight="1" s="183">
       <c r="A130" s="2" t="inlineStr">
         <is>
           <t>Disponibilità Liquide Peso</t>
@@ -5437,7 +5459,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="131" ht="15" customHeight="1">
+    <row r="131" ht="15" customHeight="1" s="183">
       <c r="A131" s="2" t="inlineStr">
         <is>
           <t>Crescita Disponibilità liquide</t>
@@ -5467,7 +5489,7 @@
         <v>0.35</v>
       </c>
     </row>
-    <row r="132" ht="15" customHeight="1">
+    <row r="132" ht="15" customHeight="1" s="183">
       <c r="A132" s="2" t="inlineStr">
         <is>
           <t>Disponibilità Liquide &gt; Indebitamento finanziario di breve</t>
@@ -5489,7 +5511,7 @@
       <c r="G132" s="2" t="n"/>
       <c r="H132" s="19" t="n"/>
     </row>
-    <row r="133" ht="15" customHeight="1">
+    <row r="133" ht="15" customHeight="1" s="183">
       <c r="A133" s="2" t="inlineStr">
         <is>
           <t>Disponibilità Liquide &gt; Indebitamento finanziario totale</t>
@@ -5511,7 +5533,7 @@
       <c r="G133" s="2" t="n"/>
       <c r="H133" s="2" t="n"/>
     </row>
-    <row r="134" ht="15" customHeight="1">
+    <row r="134" ht="15" customHeight="1" s="183">
       <c r="A134" s="2" t="inlineStr">
         <is>
           <t>Crescita EBITDA</t>
@@ -5542,7 +5564,7 @@
       </c>
       <c r="I134" s="8" t="n"/>
     </row>
-    <row r="135" ht="15" customHeight="1">
+    <row r="135" ht="15" customHeight="1" s="183">
       <c r="A135" s="72" t="inlineStr">
         <is>
           <t>Media</t>
@@ -5560,7 +5582,7 @@
       <c r="H135" s="17" t="n"/>
       <c r="I135" s="8" t="n"/>
     </row>
-    <row r="136" ht="15" customHeight="1">
+    <row r="136" ht="15" customHeight="1" s="183">
       <c r="A136" s="2" t="n"/>
       <c r="B136" s="2" t="n"/>
       <c r="C136" s="2" t="n"/>
@@ -5570,7 +5592,7 @@
       <c r="G136" s="2" t="n"/>
       <c r="H136" s="2" t="n"/>
     </row>
-    <row r="137" ht="15" customHeight="1">
+    <row r="137" ht="15" customHeight="1" s="183">
       <c r="A137" s="72" t="inlineStr">
         <is>
           <t>Patrimoniale</t>
@@ -5584,7 +5606,7 @@
       <c r="G137" s="72" t="n"/>
       <c r="H137" s="72" t="n"/>
     </row>
-    <row r="138" ht="15" customHeight="1">
+    <row r="138" ht="15" customHeight="1" s="183">
       <c r="A138" s="2" t="inlineStr">
         <is>
           <t>Peso Patrimonio Netto</t>
@@ -5614,7 +5636,7 @@
         <v>0.55</v>
       </c>
     </row>
-    <row r="139" ht="15" customHeight="1">
+    <row r="139" ht="15" customHeight="1" s="183">
       <c r="A139" s="2" t="inlineStr">
         <is>
           <t>Rapporto Indebitamento</t>
@@ -5644,7 +5666,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="140" ht="15" customHeight="1">
+    <row r="140" ht="15" customHeight="1" s="183">
       <c r="A140" s="72" t="inlineStr">
         <is>
           <t>Media</t>
@@ -5661,7 +5683,7 @@
       <c r="G140" s="2" t="n"/>
       <c r="H140" s="2" t="n"/>
     </row>
-    <row r="141" ht="15" customHeight="1">
+    <row r="141" ht="15" customHeight="1" s="183">
       <c r="A141" s="2" t="n"/>
       <c r="B141" s="2" t="n"/>
       <c r="C141" s="2" t="n"/>
@@ -5671,7 +5693,7 @@
       <c r="G141" s="2" t="n"/>
       <c r="H141" s="2" t="n"/>
     </row>
-    <row r="142" ht="15" customHeight="1">
+    <row r="142" ht="15" customHeight="1" s="183">
       <c r="A142" s="2" t="n"/>
       <c r="B142" s="2" t="n"/>
       <c r="C142" s="2" t="n"/>
@@ -5681,7 +5703,7 @@
       <c r="G142" s="2" t="n"/>
       <c r="H142" s="2" t="n"/>
     </row>
-    <row r="143" ht="15" customHeight="1">
+    <row r="143" ht="15" customHeight="1" s="183">
       <c r="A143" s="2" t="n"/>
       <c r="B143" s="2" t="n"/>
       <c r="C143" s="2" t="n"/>
@@ -5758,38 +5780,38 @@
   <dimension ref="A1:H185"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.875" defaultRowHeight="14.25"/>
   <cols>
-    <col width="33.625" customWidth="1" min="1" max="1"/>
-    <col width="22.125" customWidth="1" min="2" max="3"/>
-    <col width="27.875" customWidth="1" min="4" max="4"/>
-    <col width="11.875" customWidth="1" min="6" max="6"/>
-    <col width="44.625" customWidth="1" min="7" max="7"/>
-    <col width="14.875" customWidth="1" min="9" max="9"/>
-    <col width="14.625" customWidth="1" min="10" max="10"/>
+    <col width="33.625" customWidth="1" style="183" min="1" max="1"/>
+    <col width="22.125" customWidth="1" style="183" min="2" max="3"/>
+    <col width="27.875" customWidth="1" style="183" min="4" max="4"/>
+    <col width="11.875" customWidth="1" style="183" min="6" max="6"/>
+    <col width="44.625" customWidth="1" style="183" min="7" max="7"/>
+    <col width="14.875" customWidth="1" style="183" min="9" max="9"/>
+    <col width="14.625" customWidth="1" style="183" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="35.1" customHeight="1">
-      <c r="A1" s="125" t="n"/>
-      <c r="B1" s="173">
+    <row r="1" ht="35.1" customHeight="1" s="183">
+      <c r="A1" s="111" t="n"/>
+      <c r="B1" s="139">
         <f>Input!B1</f>
         <v/>
       </c>
-      <c r="C1" s="123" t="n"/>
-      <c r="D1" s="123" t="n"/>
-      <c r="E1" s="123" t="n"/>
-      <c r="F1" s="190" t="n"/>
+      <c r="C1" s="110" t="n"/>
+      <c r="D1" s="110" t="n"/>
+      <c r="E1" s="110" t="n"/>
+      <c r="F1" s="189" t="n"/>
       <c r="G1" s="12" t="n"/>
       <c r="H1" s="12" t="n"/>
     </row>
-    <row r="2" ht="11.45" customHeight="1">
+    <row r="2" ht="11.45" customHeight="1" s="183">
       <c r="A2" s="79" t="n"/>
       <c r="B2" s="80" t="n"/>
       <c r="C2" s="78" t="n"/>
       <c r="D2" s="80" t="n"/>
       <c r="E2" s="78" t="n"/>
-      <c r="F2" s="191" t="n"/>
-    </row>
-    <row r="3" ht="18.95" customHeight="1" thickBot="1">
-      <c r="A3" s="126" t="inlineStr">
+      <c r="F2" s="190" t="n"/>
+    </row>
+    <row r="3" ht="18.95" customHeight="1" s="183" thickBot="1">
+      <c r="A3" s="112" t="inlineStr">
         <is>
           <t>Profilo Società</t>
         </is>
@@ -5798,9 +5820,9 @@
       <c r="C3" s="78" t="n"/>
       <c r="D3" s="80" t="n"/>
       <c r="E3" s="78" t="n"/>
-      <c r="F3" s="82" t="n"/>
-    </row>
-    <row r="4" ht="21" customHeight="1" thickTop="1">
+      <c r="F3" s="81" t="n"/>
+    </row>
+    <row r="4" ht="21" customHeight="1" s="183" thickTop="1">
       <c r="A4" s="78" t="inlineStr">
         <is>
           <t>PARTITA IVA</t>
@@ -5815,7 +5837,7 @@
       <c r="E4" s="78" t="n"/>
       <c r="F4" s="78" t="n"/>
     </row>
-    <row r="5" ht="18.75" customHeight="1">
+    <row r="5" ht="18.75" customHeight="1" s="183">
       <c r="A5" s="78" t="inlineStr">
         <is>
           <t>ATECO 2007</t>
@@ -5826,7 +5848,7 @@
         <v/>
       </c>
       <c r="C5" s="78" t="n"/>
-      <c r="D5" s="117" t="inlineStr">
+      <c r="D5" s="104" t="inlineStr">
         <is>
           <t>Fido</t>
         </is>
@@ -5834,7 +5856,7 @@
       <c r="E5" s="78" t="n"/>
       <c r="F5" s="78" t="n"/>
     </row>
-    <row r="6" ht="18.75" customHeight="1">
+    <row r="6" ht="18.75" customHeight="1" s="183">
       <c r="A6" s="78" t="inlineStr">
         <is>
           <t>FORMA GIURIDICA</t>
@@ -5845,14 +5867,14 @@
         <v/>
       </c>
       <c r="C6" s="78" t="n"/>
-      <c r="D6" s="192">
+      <c r="D6" s="191">
         <f>IF(Input!E2="",Input!$D$85,Input!$E$2)</f>
         <v/>
       </c>
       <c r="E6" s="78" t="n"/>
       <c r="F6" s="78" t="n"/>
     </row>
-    <row r="7" ht="18.75" customHeight="1">
+    <row r="7" ht="18.75" customHeight="1" s="183">
       <c r="A7" s="78" t="inlineStr">
         <is>
           <t>SEDE</t>
@@ -5867,7 +5889,7 @@
       <c r="E7" s="78" t="n"/>
       <c r="F7" s="78" t="n"/>
     </row>
-    <row r="8" ht="11.1" customHeight="1">
+    <row r="8" ht="11.1" customHeight="1" s="183">
       <c r="A8" s="78" t="n"/>
       <c r="B8" s="78" t="n"/>
       <c r="C8" s="78" t="n"/>
@@ -5875,92 +5897,91 @@
       <c r="E8" s="78" t="n"/>
       <c r="F8" s="78" t="n"/>
     </row>
-    <row r="9" ht="9.6" customHeight="1" thickBot="1">
+    <row r="9" ht="9.6" customHeight="1" s="183" thickBot="1">
       <c r="A9" s="78" t="n"/>
       <c r="B9" s="78" t="n"/>
       <c r="D9" s="78" t="n"/>
       <c r="E9" s="78" t="n"/>
       <c r="F9" s="78" t="n"/>
     </row>
-    <row r="10" ht="18" customHeight="1" thickBot="1">
-      <c r="A10" s="116" t="inlineStr">
+    <row r="10" ht="18" customHeight="1" s="183" thickBot="1">
+      <c r="A10" s="103" t="inlineStr">
         <is>
           <t>Situazione Reddituale</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="26.25" customHeight="1" thickBot="1">
-      <c r="A11" s="193">
+    <row r="11" ht="26.25" customHeight="1" s="183" thickBot="1">
+      <c r="A11" s="187">
         <f>IF(B11="Eccellente","nnnnnnnnnnnnn",IF(B11="Positiva","nnnnnnnnnn",IF(B11="Adeguata","nnnnnnn",IF(B11="Critica","nnnn",IF(B11="Molto Critica","n","")))))</f>
         <v/>
       </c>
-      <c r="B11" s="83" t="inlineStr">
+      <c r="B11" s="82" t="inlineStr">
         <is>
           <t>Adeguata</t>
         </is>
       </c>
-      <c r="D11" s="117" t="inlineStr">
+      <c r="D11" s="104" t="inlineStr">
         <is>
           <t>Grade</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="18.95" customHeight="1" thickBot="1">
+    <row r="12" ht="18.95" customHeight="1" s="183" thickBot="1">
       <c r="A12" s="10" t="n"/>
       <c r="B12" s="7" t="n"/>
       <c r="D12" s="7" t="n"/>
     </row>
-    <row r="13" ht="18" customHeight="1" thickBot="1">
-      <c r="A13" s="116" t="inlineStr">
+    <row r="13" ht="18" customHeight="1" s="183" thickBot="1">
+      <c r="A13" s="103" t="inlineStr">
         <is>
           <t>Situazione Finanziaria</t>
         </is>
       </c>
       <c r="D13" s="14" t="n"/>
     </row>
-    <row r="14" ht="26.25" customHeight="1" thickBot="1">
-      <c r="A14" s="193">
+    <row r="14" ht="26.25" customHeight="1" s="183" thickBot="1">
+      <c r="A14" s="187">
         <f>IF(B14="Eccellente","nnnnnnnnnnnnn",IF(B14="Positiva","nnnnnnnnnn",IF(B14="Adeguata","nnnnnnn",IF(B14="Critica","nnnn",IF(B14="Molto Critica","n","")))))</f>
         <v/>
       </c>
-      <c r="B14" s="83" t="n"/>
+      <c r="B14" s="82" t="n"/>
       <c r="D14" s="14" t="n"/>
     </row>
-    <row r="15" ht="24" customHeight="1" thickBot="1">
+    <row r="15" ht="24" customHeight="1" s="183" thickBot="1">
       <c r="A15" s="10" t="n"/>
       <c r="B15" s="7" t="n"/>
-      <c r="D15" s="194">
+      <c r="D15" s="192">
         <f>IF(Input!D2="",Input!$C$83,Input!$D$2)</f>
         <v/>
       </c>
     </row>
-    <row r="16" ht="17.1" customHeight="1" thickBot="1">
-      <c r="A16" s="116" t="inlineStr">
+    <row r="16" ht="17.1" customHeight="1" s="183" thickBot="1">
+      <c r="A16" s="103" t="inlineStr">
         <is>
           <t>Situazione Patrimoniale</t>
         </is>
       </c>
       <c r="D16" s="15" t="n"/>
     </row>
-    <row r="17" ht="24" customHeight="1" thickBot="1">
-      <c r="A17" s="193">
+    <row r="17" ht="24" customHeight="1" s="183" thickBot="1">
+      <c r="A17" s="187">
         <f>IF(B17="Eccellente","nnnnnnnnnnnnn",IF(B17="Positiva","nnnnnnnnnn",IF(B17="Adeguata","nnnnnnn",IF(B17="Critica","nnnn",IF(B17="Molto Critica","n","")))))</f>
         <v/>
       </c>
-      <c r="B17" s="83" t="inlineStr">
+      <c r="B17" s="82" t="inlineStr">
         <is>
           <t>Adeguata</t>
         </is>
       </c>
       <c r="D17" s="15" t="n"/>
     </row>
-    <row r="18"/>
-    <row r="19" ht="9" customHeight="1">
+    <row r="19" ht="9" customHeight="1" s="183">
       <c r="A19" s="13" t="n"/>
       <c r="B19" s="13" t="n"/>
     </row>
-    <row r="20" ht="18" customHeight="1" thickBot="1">
-      <c r="A20" s="176" t="inlineStr">
+    <row r="20" ht="18" customHeight="1" s="183" thickBot="1">
+      <c r="A20" s="141" t="inlineStr">
         <is>
           <t>Sintesi KPI</t>
         </is>
@@ -5970,343 +5991,343 @@
         <v/>
       </c>
     </row>
-    <row r="21" ht="15" customHeight="1" thickTop="1">
+    <row r="21" ht="15" customHeight="1" s="183" thickTop="1">
       <c r="A21" s="13" t="n"/>
       <c r="B21" s="13" t="n"/>
     </row>
-    <row r="22" ht="20.1" customHeight="1">
-      <c r="A22" s="130" t="inlineStr">
+    <row r="22" ht="20.1" customHeight="1" s="183">
+      <c r="A22" s="116" t="inlineStr">
         <is>
           <t>Ricavi</t>
         </is>
       </c>
-      <c r="B22" s="130" t="inlineStr">
+      <c r="B22" s="116" t="inlineStr">
         <is>
           <t>EBIT</t>
         </is>
       </c>
-      <c r="C22" s="130" t="inlineStr">
+      <c r="C22" s="116" t="inlineStr">
         <is>
           <t>EBITDA</t>
         </is>
       </c>
-      <c r="D22" s="130" t="inlineStr">
+      <c r="D22" s="116" t="inlineStr">
         <is>
           <t>Utile d'es.</t>
         </is>
       </c>
-      <c r="E22" s="128" t="n"/>
-      <c r="F22" s="128" t="n"/>
-    </row>
-    <row r="23" ht="29.1" customHeight="1">
-      <c r="A23" s="195">
+      <c r="E22" s="114" t="n"/>
+      <c r="F22" s="114" t="n"/>
+    </row>
+    <row r="23" ht="29.1" customHeight="1" s="183">
+      <c r="A23" s="193">
         <f>+Input!B8</f>
         <v/>
       </c>
-      <c r="B23" s="195">
+      <c r="B23" s="193">
         <f>+Input!B17</f>
         <v/>
       </c>
-      <c r="C23" s="195">
+      <c r="C23" s="193">
         <f>+Input!B17+Input!B14</f>
         <v/>
       </c>
-      <c r="D23" s="195">
+      <c r="D23" s="193">
         <f>+Input!B20</f>
         <v/>
       </c>
-      <c r="E23" s="128" t="n"/>
-      <c r="F23" s="128" t="n"/>
-    </row>
-    <row r="24" ht="29.1" customHeight="1">
-      <c r="A24" s="132">
+      <c r="E23" s="114" t="n"/>
+      <c r="F23" s="114" t="n"/>
+    </row>
+    <row r="24" ht="29.1" customHeight="1" s="183">
+      <c r="A24" s="117">
         <f>IFERROR(TEXT((Input!B8-Input!C8)/Input!C8,"[$-410]+0.00%;[$-410]-0.00%;[$-410]0.00%") &amp; " vs " &amp; TEXT(Input!C8,"[$-410]#,##0"),"n.d.")</f>
         <v/>
       </c>
-      <c r="B24" s="132">
+      <c r="B24" s="117">
         <f>IFERROR(TEXT((Input!B17-Input!C17)/Input!C17,"[$-410]+0.00%;[$-410]-0.00%;[$-410]0.00%") &amp; " vs " &amp; TEXT(Input!C17,"[$-410]#,##0"),"n.d.")</f>
         <v/>
       </c>
-      <c r="C24" s="132">
+      <c r="C24" s="117">
         <f>IFERROR(TEXT(((Input!B17+Input!B14)-(Input!C17+Input!C14))/(Input!C17+Input!C14),"[$-410]+0.00%;[$-410]-0.00%;[$-410]0.00%") &amp; " vs " &amp; TEXT((Input!C17+Input!C14),"[$-410]#,##0"),"n.d.")</f>
         <v/>
       </c>
-      <c r="D24" s="132">
+      <c r="D24" s="117">
         <f>IFERROR(TEXT((Input!B20-Input!C20)/Input!C20,"[$-410]+0.00%;[$-410]-0.00%;[$-410]0.00%") &amp; " vs " &amp; TEXT(Input!C20,"[$-410]#,##0"),"n.d.")</f>
         <v/>
       </c>
-      <c r="E24" s="128" t="n"/>
-      <c r="F24" s="128" t="n"/>
-    </row>
-    <row r="25" ht="14.45" customHeight="1">
-      <c r="A25" s="132" t="n"/>
-      <c r="B25" s="132" t="n"/>
-      <c r="C25" s="132" t="n"/>
-      <c r="D25" s="132" t="n"/>
-      <c r="E25" s="128" t="n"/>
-      <c r="F25" s="128" t="n"/>
-    </row>
-    <row r="26" ht="23.1" customHeight="1">
-      <c r="A26" s="130" t="inlineStr">
+      <c r="E24" s="114" t="n"/>
+      <c r="F24" s="114" t="n"/>
+    </row>
+    <row r="25" ht="14.45" customHeight="1" s="183">
+      <c r="A25" s="117" t="n"/>
+      <c r="B25" s="117" t="n"/>
+      <c r="C25" s="117" t="n"/>
+      <c r="D25" s="117" t="n"/>
+      <c r="E25" s="114" t="n"/>
+      <c r="F25" s="114" t="n"/>
+    </row>
+    <row r="26" ht="23.1" customHeight="1" s="183">
+      <c r="A26" s="116" t="inlineStr">
         <is>
           <t>Patr. Netto</t>
         </is>
       </c>
-      <c r="B26" s="130" t="inlineStr">
+      <c r="B26" s="116" t="inlineStr">
         <is>
           <t>Deb. Fin.</t>
         </is>
       </c>
-      <c r="C26" s="130" t="inlineStr">
+      <c r="C26" s="116" t="inlineStr">
         <is>
           <t>Disp. Liq.</t>
         </is>
       </c>
-      <c r="D26" s="130" t="inlineStr">
+      <c r="D26" s="116" t="inlineStr">
         <is>
           <t>Dipendenti</t>
         </is>
       </c>
-      <c r="E26" s="128" t="n"/>
-      <c r="F26" s="128" t="n"/>
-    </row>
-    <row r="27" ht="29.1" customHeight="1">
-      <c r="A27" s="196">
+      <c r="E26" s="114" t="n"/>
+      <c r="F26" s="114" t="n"/>
+    </row>
+    <row r="27" ht="29.1" customHeight="1" s="183">
+      <c r="A27" s="194">
         <f>+Input!B34</f>
         <v/>
       </c>
-      <c r="B27" s="196">
+      <c r="B27" s="194">
         <f>+Input!B40</f>
         <v/>
       </c>
-      <c r="C27" s="196">
+      <c r="C27" s="194">
         <f>+Input!B31</f>
         <v/>
       </c>
-      <c r="D27" s="134">
+      <c r="D27" s="118">
         <f>+Input!B21</f>
         <v/>
       </c>
-      <c r="E27" s="128" t="n"/>
-      <c r="F27" s="128" t="n"/>
-    </row>
-    <row r="28" ht="29.1" customHeight="1">
-      <c r="A28" s="132">
+      <c r="E27" s="114" t="n"/>
+      <c r="F27" s="114" t="n"/>
+    </row>
+    <row r="28" ht="29.1" customHeight="1" s="183">
+      <c r="A28" s="117">
         <f>IFERROR(TEXT((Input!B34-Input!C34)/Input!C34,"[$-410]+0.00%;[$-410]-0.00%;[$-410]0.00%") &amp; " vs " &amp; TEXT(Input!C34,"[$-410]#,##0"),"n.d.")</f>
         <v/>
       </c>
-      <c r="B28" s="132">
+      <c r="B28" s="117">
         <f>IFERROR(TEXT((Input!B40-Input!C40)/Input!C40,"[$-410]+0.00%;[$-410]-0.00%;[$-410]0.00%")&amp;" vs "&amp;TEXT(Input!C40,"[$-410]#,##0"),"n.d.")</f>
         <v/>
       </c>
-      <c r="C28" s="132">
+      <c r="C28" s="117">
         <f>IFERROR(TEXT((Input!B31-Input!C31)/Input!C31,"[$-410]+0.00%;[$-410]-0.00%;[$-410]0.00%") &amp; " vs " &amp; TEXT(Input!C31,"[$-410]#,##0"),"n.d.")</f>
         <v/>
       </c>
-      <c r="D28" s="132">
+      <c r="D28" s="117">
         <f>IFERROR(TEXT((Input!B21-Input!C21)/Input!C21,"[$-410]+0.00%;[$-410]-0.00%;[$-410]0.00%") &amp; " vs " &amp; TEXT(Input!C21,"[$-410]#,##0"),"n.d.")</f>
         <v/>
       </c>
-      <c r="E28" s="128" t="n"/>
-      <c r="F28" s="128" t="n"/>
-    </row>
-    <row r="29" ht="9" customHeight="1">
-      <c r="A29" s="128" t="n"/>
-      <c r="B29" s="128" t="n"/>
-      <c r="C29" s="128" t="n"/>
-      <c r="D29" s="128" t="n"/>
-      <c r="E29" s="128" t="n"/>
-      <c r="F29" s="128" t="n"/>
-    </row>
-    <row r="30" ht="11.1" customHeight="1">
-      <c r="A30" s="128" t="n"/>
-      <c r="B30" s="128" t="n"/>
-      <c r="C30" s="128" t="n"/>
-      <c r="D30" s="128" t="n"/>
-      <c r="E30" s="128" t="n"/>
-      <c r="F30" s="128" t="n"/>
-    </row>
-    <row r="31" ht="21" customHeight="1" thickBot="1">
-      <c r="A31" s="126" t="inlineStr">
+      <c r="E28" s="114" t="n"/>
+      <c r="F28" s="114" t="n"/>
+    </row>
+    <row r="29" ht="9" customHeight="1" s="183">
+      <c r="A29" s="114" t="n"/>
+      <c r="B29" s="114" t="n"/>
+      <c r="C29" s="114" t="n"/>
+      <c r="D29" s="114" t="n"/>
+      <c r="E29" s="114" t="n"/>
+      <c r="F29" s="114" t="n"/>
+    </row>
+    <row r="30" ht="11.1" customHeight="1" s="183">
+      <c r="A30" s="114" t="n"/>
+      <c r="B30" s="114" t="n"/>
+      <c r="C30" s="114" t="n"/>
+      <c r="D30" s="114" t="n"/>
+      <c r="E30" s="114" t="n"/>
+      <c r="F30" s="114" t="n"/>
+    </row>
+    <row r="31" ht="21" customHeight="1" s="183" thickBot="1">
+      <c r="A31" s="112" t="inlineStr">
         <is>
           <t>Valutazione</t>
         </is>
       </c>
-      <c r="B31" s="128" t="n"/>
-      <c r="E31" s="128" t="n"/>
-      <c r="F31" s="128" t="n"/>
-    </row>
-    <row r="32" ht="12.6" customHeight="1" thickTop="1">
-      <c r="A32" s="128" t="n"/>
-      <c r="B32" s="128" t="n"/>
-      <c r="C32" s="128" t="n"/>
-      <c r="D32" s="128" t="n"/>
-      <c r="E32" s="128" t="n"/>
-      <c r="F32" s="128" t="n"/>
-    </row>
-    <row r="33" ht="17.45" customHeight="1">
-      <c r="A33" s="135" t="inlineStr">
+      <c r="B31" s="114" t="n"/>
+      <c r="E31" s="114" t="n"/>
+      <c r="F31" s="114" t="n"/>
+    </row>
+    <row r="32" ht="12.6" customHeight="1" s="183" thickTop="1">
+      <c r="A32" s="114" t="n"/>
+      <c r="B32" s="114" t="n"/>
+      <c r="C32" s="114" t="n"/>
+      <c r="D32" s="114" t="n"/>
+      <c r="E32" s="114" t="n"/>
+      <c r="F32" s="114" t="n"/>
+    </row>
+    <row r="33" ht="17.45" customHeight="1" s="183">
+      <c r="A33" s="119" t="inlineStr">
         <is>
           <t xml:space="preserve">   Ambito Economico</t>
         </is>
       </c>
-      <c r="B33" s="135" t="n"/>
-      <c r="C33" s="135" t="inlineStr">
+      <c r="B33" s="119" t="n"/>
+      <c r="C33" s="119" t="inlineStr">
         <is>
           <t>Ambito Finanziario e Patrimoniale</t>
         </is>
       </c>
-      <c r="D33" s="135" t="n"/>
-      <c r="E33" s="128" t="n"/>
-      <c r="F33" s="128" t="n"/>
-    </row>
-    <row r="34" ht="17.45" customHeight="1">
-      <c r="A34" s="197" t="n"/>
-      <c r="C34" s="197" t="n"/>
-      <c r="E34" s="128" t="n"/>
-      <c r="F34" s="128" t="n"/>
-    </row>
-    <row r="35" ht="17.1" customHeight="1">
-      <c r="E35" s="128" t="n"/>
-      <c r="F35" s="128" t="n"/>
-    </row>
-    <row r="36" ht="17.1" customHeight="1">
-      <c r="E36" s="128" t="n"/>
-      <c r="F36" s="128" t="n"/>
-    </row>
-    <row r="37" ht="17.1" customHeight="1">
-      <c r="E37" s="128" t="n"/>
-      <c r="F37" s="128" t="n"/>
-    </row>
-    <row r="38" ht="17.1" customHeight="1">
-      <c r="E38" s="128" t="n"/>
-      <c r="F38" s="128" t="n"/>
-    </row>
-    <row r="39" ht="17.1" customHeight="1">
-      <c r="E39" s="128" t="n"/>
-      <c r="F39" s="128" t="n"/>
-    </row>
-    <row r="40" ht="17.1" customHeight="1">
-      <c r="E40" s="128" t="n"/>
-      <c r="F40" s="128" t="n"/>
-    </row>
-    <row r="41" ht="17.1" customHeight="1">
-      <c r="E41" s="128" t="n"/>
-      <c r="F41" s="128" t="n"/>
-    </row>
-    <row r="42" ht="12" customHeight="1">
-      <c r="E42" s="128" t="n"/>
-      <c r="F42" s="128" t="n"/>
-    </row>
-    <row r="43" ht="15" customHeight="1">
+      <c r="D33" s="119" t="n"/>
+      <c r="E33" s="114" t="n"/>
+      <c r="F33" s="114" t="n"/>
+    </row>
+    <row r="34" ht="17.45" customHeight="1" s="183">
+      <c r="A34" s="182" t="n"/>
+      <c r="C34" s="182" t="n"/>
+      <c r="E34" s="114" t="n"/>
+      <c r="F34" s="114" t="n"/>
+    </row>
+    <row r="35" ht="17.1" customHeight="1" s="183">
+      <c r="E35" s="114" t="n"/>
+      <c r="F35" s="114" t="n"/>
+    </row>
+    <row r="36" ht="17.1" customHeight="1" s="183">
+      <c r="E36" s="114" t="n"/>
+      <c r="F36" s="114" t="n"/>
+    </row>
+    <row r="37" ht="17.1" customHeight="1" s="183">
+      <c r="E37" s="114" t="n"/>
+      <c r="F37" s="114" t="n"/>
+    </row>
+    <row r="38" ht="17.1" customHeight="1" s="183">
+      <c r="E38" s="114" t="n"/>
+      <c r="F38" s="114" t="n"/>
+    </row>
+    <row r="39" ht="17.1" customHeight="1" s="183">
+      <c r="E39" s="114" t="n"/>
+      <c r="F39" s="114" t="n"/>
+    </row>
+    <row r="40" ht="17.1" customHeight="1" s="183">
+      <c r="E40" s="114" t="n"/>
+      <c r="F40" s="114" t="n"/>
+    </row>
+    <row r="41" ht="17.1" customHeight="1" s="183">
+      <c r="E41" s="114" t="n"/>
+      <c r="F41" s="114" t="n"/>
+    </row>
+    <row r="42" ht="12" customHeight="1" s="183">
+      <c r="E42" s="114" t="n"/>
+      <c r="F42" s="114" t="n"/>
+    </row>
+    <row r="43" ht="15" customHeight="1" s="183">
       <c r="E43" s="78" t="n"/>
       <c r="F43" s="78" t="n"/>
     </row>
-    <row r="44" ht="17.1" customHeight="1">
+    <row r="44" ht="17.1" customHeight="1" s="183">
       <c r="E44" s="78" t="n"/>
       <c r="F44" s="78" t="n"/>
     </row>
-    <row r="45" ht="17.1" customHeight="1">
-      <c r="A45" s="198" t="inlineStr">
+    <row r="45" ht="17.1" customHeight="1" s="183">
+      <c r="A45" s="195" t="inlineStr">
         <is>
           <t>Sintesi</t>
         </is>
       </c>
-      <c r="B45" s="172" t="n"/>
-      <c r="C45" s="137" t="inlineStr">
+      <c r="B45" s="138" t="n"/>
+      <c r="C45" s="121" t="inlineStr">
         <is>
           <t>Grade e Fido</t>
         </is>
       </c>
-      <c r="D45" s="137" t="n"/>
+      <c r="D45" s="121" t="n"/>
       <c r="E45" s="78" t="n"/>
       <c r="F45" s="78" t="n"/>
     </row>
-    <row r="46" ht="17.1" customHeight="1">
-      <c r="A46" s="197" t="n"/>
-      <c r="C46" s="197" t="n"/>
+    <row r="46" ht="17.1" customHeight="1" s="183">
+      <c r="A46" s="182" t="n"/>
+      <c r="C46" s="182" t="n"/>
       <c r="E46" s="78" t="n"/>
       <c r="F46" s="78" t="n"/>
     </row>
-    <row r="47" ht="17.1" customHeight="1">
+    <row r="47" ht="17.1" customHeight="1" s="183">
       <c r="E47" s="78" t="n"/>
       <c r="F47" s="78" t="n"/>
     </row>
-    <row r="48" ht="17.1" customHeight="1">
+    <row r="48" ht="17.1" customHeight="1" s="183">
       <c r="E48" s="78" t="n"/>
       <c r="F48" s="78" t="n"/>
     </row>
-    <row r="49" ht="17.1" customHeight="1">
+    <row r="49" ht="17.1" customHeight="1" s="183">
       <c r="E49" s="78" t="n"/>
       <c r="F49" s="78" t="n"/>
     </row>
-    <row r="50" ht="17.1" customHeight="1">
+    <row r="50" ht="17.1" customHeight="1" s="183">
       <c r="E50" s="78" t="n"/>
       <c r="F50" s="78" t="n"/>
     </row>
-    <row r="51" ht="17.1" customHeight="1">
+    <row r="51" ht="17.1" customHeight="1" s="183">
       <c r="E51" s="78" t="n"/>
       <c r="F51" s="78" t="n"/>
     </row>
-    <row r="52" ht="17.1" customHeight="1">
+    <row r="52" ht="17.1" customHeight="1" s="183">
       <c r="E52" s="78" t="n"/>
       <c r="F52" s="78" t="n"/>
     </row>
-    <row r="53" ht="17.1" customHeight="1">
+    <row r="53" ht="17.1" customHeight="1" s="183">
       <c r="E53" s="78" t="n"/>
       <c r="F53" s="78" t="n"/>
     </row>
-    <row r="54" ht="17.1" customHeight="1">
+    <row r="54" ht="17.1" customHeight="1" s="183">
       <c r="E54" s="78" t="n"/>
       <c r="F54" s="78" t="n"/>
     </row>
-    <row r="55" ht="20.45" customHeight="1">
+    <row r="55" ht="20.45" customHeight="1" s="183">
       <c r="E55" s="78" t="n"/>
       <c r="F55" s="78" t="n"/>
     </row>
-    <row r="56" ht="8.1" customHeight="1">
-      <c r="A56" s="175" t="n"/>
-      <c r="B56" s="175" t="n"/>
-      <c r="C56" s="175" t="n"/>
-      <c r="D56" s="175" t="n"/>
+    <row r="56" ht="8.1" customHeight="1" s="183">
+      <c r="A56" s="140" t="n"/>
+      <c r="B56" s="140" t="n"/>
+      <c r="C56" s="140" t="n"/>
+      <c r="D56" s="140" t="n"/>
       <c r="E56" s="78" t="n"/>
       <c r="F56" s="78" t="n"/>
     </row>
-    <row r="57" ht="26.1" customHeight="1">
-      <c r="A57" s="115" t="n"/>
-      <c r="B57" s="115" t="n"/>
-      <c r="C57" s="115" t="n"/>
-      <c r="D57" s="115" t="n"/>
+    <row r="57" ht="26.1" customHeight="1" s="183">
+      <c r="A57" s="102" t="n"/>
+      <c r="B57" s="102" t="n"/>
+      <c r="C57" s="102" t="n"/>
+      <c r="D57" s="102" t="n"/>
       <c r="E57" s="78" t="n"/>
       <c r="F57" s="78" t="n"/>
     </row>
-    <row r="58" ht="20.1" customHeight="1">
-      <c r="A58" s="118" t="inlineStr">
+    <row r="58" ht="20.1" customHeight="1" s="183">
+      <c r="A58" s="105" t="inlineStr">
         <is>
           <t>STATO PATRIMONIALE</t>
         </is>
       </c>
-      <c r="B58" s="119" t="n"/>
-      <c r="C58" s="119" t="n"/>
-      <c r="D58" s="119" t="n"/>
+      <c r="B58" s="106" t="n"/>
+      <c r="C58" s="106" t="n"/>
+      <c r="D58" s="106" t="n"/>
       <c r="E58" s="78" t="n"/>
       <c r="F58" s="78" t="n"/>
     </row>
-    <row r="59" ht="18.6" customHeight="1">
-      <c r="A59" s="138" t="inlineStr">
+    <row r="59" ht="18.6" customHeight="1" s="183">
+      <c r="A59" s="122" t="inlineStr">
         <is>
           <t>Voce</t>
         </is>
       </c>
-      <c r="B59" s="142">
+      <c r="B59" s="125">
         <f>Input!$B$6</f>
         <v/>
       </c>
-      <c r="C59" s="142">
+      <c r="C59" s="125">
         <f>Input!$C$6</f>
         <v/>
       </c>
-      <c r="D59" s="142" t="inlineStr">
+      <c r="D59" s="125" t="inlineStr">
         <is>
           <t>Var %</t>
         </is>
@@ -6314,662 +6335,662 @@
       <c r="E59" s="78" t="n"/>
       <c r="F59" s="78" t="n"/>
     </row>
-    <row r="60" ht="15" customHeight="1">
-      <c r="A60" s="140" t="inlineStr">
+    <row r="60" ht="15" customHeight="1" s="183">
+      <c r="A60" s="123" t="inlineStr">
         <is>
           <t>Attivo</t>
         </is>
       </c>
-      <c r="B60" s="141" t="n"/>
-      <c r="C60" s="141" t="n"/>
-      <c r="D60" s="141" t="n"/>
+      <c r="B60" s="124" t="n"/>
+      <c r="C60" s="124" t="n"/>
+      <c r="D60" s="124" t="n"/>
       <c r="E60" s="78" t="n"/>
       <c r="F60" s="78" t="n"/>
     </row>
-    <row r="61" ht="15" customHeight="1">
-      <c r="A61" s="86" t="inlineStr">
+    <row r="61" ht="15" customHeight="1" s="183">
+      <c r="A61" s="85" t="inlineStr">
         <is>
           <t xml:space="preserve">Immobilizzazioni </t>
         </is>
       </c>
-      <c r="B61" s="199">
+      <c r="B61" s="196">
         <f>Input!B27</f>
         <v/>
       </c>
-      <c r="C61" s="199">
+      <c r="C61" s="196">
         <f>Input!C27</f>
         <v/>
       </c>
-      <c r="D61" s="200">
+      <c r="D61" s="197">
         <f>IFERROR((B61-C61)/C61,"")</f>
         <v/>
       </c>
       <c r="E61" s="78" t="n"/>
       <c r="F61" s="78" t="n"/>
     </row>
-    <row r="62" ht="15" customHeight="1">
-      <c r="A62" s="88" t="inlineStr">
+    <row r="62" ht="15" customHeight="1" s="183">
+      <c r="A62" s="86" t="inlineStr">
         <is>
           <t>% Immob. su attivo</t>
         </is>
       </c>
-      <c r="B62" s="201">
+      <c r="B62" s="198">
         <f>B$61/B$73</f>
         <v/>
       </c>
-      <c r="C62" s="201">
+      <c r="C62" s="198">
         <f>C$61/C$73</f>
         <v/>
       </c>
-      <c r="D62" s="90" t="n"/>
+      <c r="D62" s="87" t="n"/>
       <c r="E62" s="78" t="n"/>
       <c r="F62" s="78" t="n"/>
     </row>
-    <row r="63" ht="15" customHeight="1">
-      <c r="A63" s="86" t="inlineStr">
+    <row r="63" ht="15" customHeight="1" s="183">
+      <c r="A63" s="85" t="inlineStr">
         <is>
           <t>Rimanenze</t>
         </is>
       </c>
-      <c r="B63" s="199">
+      <c r="B63" s="196">
         <f>Input!B28</f>
         <v/>
       </c>
-      <c r="C63" s="199">
+      <c r="C63" s="196">
         <f>Input!C28</f>
         <v/>
       </c>
-      <c r="D63" s="200">
+      <c r="D63" s="197">
         <f>IFERROR((B63-C63)/C63,"")</f>
         <v/>
       </c>
       <c r="E63" s="78" t="n"/>
       <c r="F63" s="78" t="n"/>
     </row>
-    <row r="64" ht="15" customHeight="1">
-      <c r="A64" s="88" t="inlineStr">
+    <row r="64" ht="15" customHeight="1" s="183">
+      <c r="A64" s="86" t="inlineStr">
         <is>
           <t>% Rimanenze su attivo</t>
         </is>
       </c>
-      <c r="B64" s="201">
+      <c r="B64" s="198">
         <f>B$63/B$73</f>
         <v/>
       </c>
-      <c r="C64" s="201">
+      <c r="C64" s="198">
         <f>C$63/C$73</f>
         <v/>
       </c>
-      <c r="D64" s="90" t="n"/>
+      <c r="D64" s="87" t="n"/>
       <c r="E64" s="78" t="n"/>
       <c r="F64" s="78" t="n"/>
     </row>
-    <row r="65" ht="15" customHeight="1">
-      <c r="A65" s="86" t="inlineStr">
+    <row r="65" ht="15" customHeight="1" s="183">
+      <c r="A65" s="85" t="inlineStr">
         <is>
           <t>Crediti</t>
         </is>
       </c>
-      <c r="B65" s="199">
+      <c r="B65" s="196">
         <f>Input!B29</f>
         <v/>
       </c>
-      <c r="C65" s="199">
+      <c r="C65" s="196">
         <f>Input!C29</f>
         <v/>
       </c>
-      <c r="D65" s="200">
+      <c r="D65" s="197">
         <f>IFERROR((B65-C65)/C65,"")</f>
         <v/>
       </c>
       <c r="E65" s="78" t="n"/>
       <c r="F65" s="78" t="n"/>
     </row>
-    <row r="66" ht="15" customHeight="1">
-      <c r="A66" s="88" t="inlineStr">
+    <row r="66" ht="15" customHeight="1" s="183">
+      <c r="A66" s="86" t="inlineStr">
         <is>
           <t>% Crediti su attivo</t>
         </is>
       </c>
-      <c r="B66" s="201">
+      <c r="B66" s="198">
         <f>B$65/B$73</f>
         <v/>
       </c>
-      <c r="C66" s="201">
+      <c r="C66" s="198">
         <f>C$65/C$73</f>
         <v/>
       </c>
-      <c r="D66" s="90" t="n"/>
+      <c r="D66" s="87" t="n"/>
       <c r="E66" s="78" t="n"/>
       <c r="F66" s="78" t="n"/>
     </row>
-    <row r="67" ht="15" customHeight="1">
-      <c r="A67" s="86" t="inlineStr">
+    <row r="67" ht="15" customHeight="1" s="183">
+      <c r="A67" s="85" t="inlineStr">
         <is>
           <t>Attività Finanziarie</t>
         </is>
       </c>
-      <c r="B67" s="199">
+      <c r="B67" s="196">
         <f>Input!B30</f>
         <v/>
       </c>
-      <c r="C67" s="199">
+      <c r="C67" s="196">
         <f>Input!C30</f>
         <v/>
       </c>
-      <c r="D67" s="200">
+      <c r="D67" s="197">
         <f>IFERROR((B67-C67)/C67,"")</f>
         <v/>
       </c>
       <c r="E67" s="78" t="n"/>
       <c r="F67" s="78" t="n"/>
     </row>
-    <row r="68" ht="15" customHeight="1">
-      <c r="A68" s="88" t="inlineStr">
+    <row r="68" ht="15" customHeight="1" s="183">
+      <c r="A68" s="86" t="inlineStr">
         <is>
           <t>% Attivittà Finanziarie su attivo</t>
         </is>
       </c>
-      <c r="B68" s="201">
+      <c r="B68" s="198">
         <f>B$67/B$73</f>
         <v/>
       </c>
-      <c r="C68" s="201">
+      <c r="C68" s="198">
         <f>C$67/C$73</f>
         <v/>
       </c>
-      <c r="D68" s="90" t="n"/>
+      <c r="D68" s="87" t="n"/>
       <c r="E68" s="78" t="n"/>
       <c r="F68" s="78" t="n"/>
     </row>
-    <row r="69" ht="15" customHeight="1">
-      <c r="A69" s="86" t="inlineStr">
+    <row r="69" ht="15" customHeight="1" s="183">
+      <c r="A69" s="85" t="inlineStr">
         <is>
           <t>Disponibilità Liquide</t>
         </is>
       </c>
-      <c r="B69" s="199">
+      <c r="B69" s="196">
         <f>Input!B31</f>
         <v/>
       </c>
-      <c r="C69" s="199">
+      <c r="C69" s="196">
         <f>Input!C31</f>
         <v/>
       </c>
-      <c r="D69" s="200">
+      <c r="D69" s="197">
         <f>IFERROR((B69-C69)/C69,"")</f>
         <v/>
       </c>
       <c r="E69" s="78" t="n"/>
       <c r="F69" s="78" t="n"/>
     </row>
-    <row r="70" ht="15" customHeight="1">
-      <c r="A70" s="88" t="inlineStr">
+    <row r="70" ht="15" customHeight="1" s="183">
+      <c r="A70" s="86" t="inlineStr">
         <is>
           <t>% Disp. Liq. su attivo</t>
         </is>
       </c>
-      <c r="B70" s="201">
+      <c r="B70" s="198">
         <f>B$69/B$73</f>
         <v/>
       </c>
-      <c r="C70" s="201">
+      <c r="C70" s="198">
         <f>C$69/C$73</f>
         <v/>
       </c>
-      <c r="D70" s="90" t="n"/>
+      <c r="D70" s="87" t="n"/>
       <c r="E70" s="78" t="n"/>
       <c r="F70" s="78" t="n"/>
     </row>
-    <row r="71" ht="15" customHeight="1">
-      <c r="A71" s="86" t="inlineStr">
+    <row r="71" ht="15" customHeight="1" s="183">
+      <c r="A71" s="85" t="inlineStr">
         <is>
           <t>Ratei e Risconti Attivi</t>
         </is>
       </c>
-      <c r="B71" s="199">
+      <c r="B71" s="196">
         <f>Input!B32</f>
         <v/>
       </c>
-      <c r="C71" s="199">
+      <c r="C71" s="196">
         <f>Input!C32</f>
         <v/>
       </c>
-      <c r="D71" s="200">
+      <c r="D71" s="197">
         <f>IFERROR((B71-C71)/C71,"")</f>
         <v/>
       </c>
       <c r="E71" s="78" t="n"/>
       <c r="F71" s="78" t="n"/>
     </row>
-    <row r="72" ht="15.95" customHeight="1" thickBot="1">
-      <c r="A72" s="91" t="inlineStr">
+    <row r="72" ht="15.95" customHeight="1" s="183" thickBot="1">
+      <c r="A72" s="88" t="inlineStr">
         <is>
           <t>% Ratei e Risconti attivi su attivo</t>
         </is>
       </c>
-      <c r="B72" s="202">
+      <c r="B72" s="199">
         <f>B$71/B$73</f>
         <v/>
       </c>
-      <c r="C72" s="202">
+      <c r="C72" s="199">
         <f>C$71/C$73</f>
         <v/>
       </c>
-      <c r="D72" s="93" t="n"/>
+      <c r="D72" s="89" t="n"/>
       <c r="E72" s="78" t="n"/>
       <c r="F72" s="78" t="n"/>
     </row>
-    <row r="73" ht="15.6" customHeight="1" thickTop="1">
-      <c r="A73" s="86" t="inlineStr">
+    <row r="73" ht="15.6" customHeight="1" s="183" thickTop="1">
+      <c r="A73" s="85" t="inlineStr">
         <is>
           <t>Totale Attivo</t>
         </is>
       </c>
-      <c r="B73" s="203">
+      <c r="B73" s="200">
         <f>Input!B33</f>
         <v/>
       </c>
-      <c r="C73" s="203">
+      <c r="C73" s="200">
         <f>Input!C33</f>
         <v/>
       </c>
-      <c r="D73" s="200">
+      <c r="D73" s="197">
         <f>IFERROR((B73-C73)/C73,"")</f>
         <v/>
       </c>
       <c r="E73" s="78" t="n"/>
       <c r="F73" s="78" t="n"/>
     </row>
-    <row r="74" ht="11.1" customHeight="1">
-      <c r="A74" s="84" t="n"/>
-      <c r="B74" s="85" t="n"/>
-      <c r="C74" s="85" t="n"/>
-      <c r="D74" s="90" t="n"/>
+    <row r="74" ht="11.1" customHeight="1" s="183">
+      <c r="A74" s="83" t="n"/>
+      <c r="B74" s="84" t="n"/>
+      <c r="C74" s="84" t="n"/>
+      <c r="D74" s="87" t="n"/>
       <c r="E74" s="78" t="n"/>
       <c r="F74" s="78" t="n"/>
     </row>
-    <row r="75" ht="15" customHeight="1">
-      <c r="A75" s="140" t="inlineStr">
+    <row r="75" ht="15" customHeight="1" s="183">
+      <c r="A75" s="123" t="inlineStr">
         <is>
           <t>Passivo</t>
         </is>
       </c>
-      <c r="B75" s="141" t="n"/>
-      <c r="C75" s="141" t="n"/>
-      <c r="D75" s="141" t="n"/>
+      <c r="B75" s="124" t="n"/>
+      <c r="C75" s="124" t="n"/>
+      <c r="D75" s="124" t="n"/>
       <c r="E75" s="78" t="n"/>
       <c r="F75" s="78" t="n"/>
     </row>
-    <row r="76" ht="15" customHeight="1">
-      <c r="A76" s="94" t="inlineStr">
+    <row r="76" ht="15" customHeight="1" s="183">
+      <c r="A76" s="90" t="inlineStr">
         <is>
           <t>Patrimonio Netto</t>
         </is>
       </c>
-      <c r="B76" s="204">
+      <c r="B76" s="201">
         <f>Input!B34</f>
         <v/>
       </c>
-      <c r="C76" s="204">
+      <c r="C76" s="201">
         <f>Input!C34</f>
         <v/>
       </c>
-      <c r="D76" s="205">
+      <c r="D76" s="202">
         <f>IFERROR((B76-C76)/C76,"")</f>
         <v/>
       </c>
       <c r="E76" s="78" t="n"/>
       <c r="F76" s="78" t="n"/>
     </row>
-    <row r="77" ht="15" customHeight="1">
-      <c r="A77" s="88" t="inlineStr">
+    <row r="77" ht="15" customHeight="1" s="183">
+      <c r="A77" s="86" t="inlineStr">
         <is>
           <t>% Tot. Patr. Netto su Tot. Passivo</t>
         </is>
       </c>
-      <c r="B77" s="201">
+      <c r="B77" s="198">
         <f>B$76/B$73</f>
         <v/>
       </c>
-      <c r="C77" s="201">
+      <c r="C77" s="198">
         <f>C$76/C$73</f>
         <v/>
       </c>
-      <c r="D77" s="90" t="n"/>
+      <c r="D77" s="87" t="n"/>
       <c r="E77" s="78" t="n"/>
       <c r="F77" s="78" t="n"/>
     </row>
-    <row r="78" ht="15" customHeight="1">
-      <c r="A78" s="86" t="inlineStr">
+    <row r="78" ht="15" customHeight="1" s="183">
+      <c r="A78" s="85" t="inlineStr">
         <is>
           <t>Fondi per rischi e oneri</t>
         </is>
       </c>
-      <c r="B78" s="199">
+      <c r="B78" s="196">
         <f>Input!B35</f>
         <v/>
       </c>
-      <c r="C78" s="199">
+      <c r="C78" s="196">
         <f>Input!C35</f>
         <v/>
       </c>
-      <c r="D78" s="200">
+      <c r="D78" s="197">
         <f>IFERROR((B78-C78)/C78,"")</f>
         <v/>
       </c>
       <c r="E78" s="78" t="n"/>
       <c r="F78" s="78" t="n"/>
     </row>
-    <row r="79" ht="15" customHeight="1">
-      <c r="A79" s="88" t="inlineStr">
+    <row r="79" ht="15" customHeight="1" s="183">
+      <c r="A79" s="86" t="inlineStr">
         <is>
           <t>% Fondi per rischi e oneri su Tot. Passivo</t>
         </is>
       </c>
-      <c r="B79" s="201">
+      <c r="B79" s="198">
         <f>B$78/B$73</f>
         <v/>
       </c>
-      <c r="C79" s="201">
+      <c r="C79" s="198">
         <f>C$78/C$73</f>
         <v/>
       </c>
-      <c r="D79" s="90" t="n"/>
+      <c r="D79" s="87" t="n"/>
       <c r="E79" s="78" t="n"/>
       <c r="F79" s="78" t="n"/>
     </row>
-    <row r="80" ht="15" customHeight="1">
-      <c r="A80" s="86" t="inlineStr">
+    <row r="80" ht="15" customHeight="1" s="183">
+      <c r="A80" s="85" t="inlineStr">
         <is>
           <t>TFR</t>
         </is>
       </c>
-      <c r="B80" s="199">
+      <c r="B80" s="196">
         <f>Input!B36</f>
         <v/>
       </c>
-      <c r="C80" s="199">
+      <c r="C80" s="196">
         <f>Input!C36</f>
         <v/>
       </c>
-      <c r="D80" s="200">
+      <c r="D80" s="197">
         <f>IFERROR((B80-C80)/C80,"")</f>
         <v/>
       </c>
       <c r="E80" s="78" t="n"/>
       <c r="F80" s="78" t="n"/>
     </row>
-    <row r="81" ht="15" customHeight="1">
-      <c r="A81" s="88" t="inlineStr">
+    <row r="81" ht="15" customHeight="1" s="183">
+      <c r="A81" s="86" t="inlineStr">
         <is>
           <t>% TFR su Tot. Passivo</t>
         </is>
       </c>
-      <c r="B81" s="201">
+      <c r="B81" s="198">
         <f>B$80/B$73</f>
         <v/>
       </c>
-      <c r="C81" s="201">
+      <c r="C81" s="198">
         <f>C$80/C$73</f>
         <v/>
       </c>
-      <c r="D81" s="90" t="n"/>
+      <c r="D81" s="87" t="n"/>
       <c r="E81" s="78" t="n"/>
       <c r="F81" s="78" t="n"/>
     </row>
-    <row r="82" ht="15" customHeight="1">
-      <c r="A82" s="86" t="inlineStr">
+    <row r="82" ht="15" customHeight="1" s="183">
+      <c r="A82" s="85" t="inlineStr">
         <is>
           <t xml:space="preserve">Debiti </t>
         </is>
       </c>
-      <c r="B82" s="199">
+      <c r="B82" s="196">
         <f>Input!E37</f>
         <v/>
       </c>
-      <c r="C82" s="199">
+      <c r="C82" s="196">
         <f>Input!F37</f>
         <v/>
       </c>
-      <c r="D82" s="200">
+      <c r="D82" s="197">
         <f>IFERROR((B82-C82)/C82,"")</f>
         <v/>
       </c>
       <c r="E82" s="78" t="n"/>
       <c r="F82" s="78" t="n"/>
     </row>
-    <row r="83" ht="15" customHeight="1">
-      <c r="A83" s="96" t="inlineStr">
+    <row r="83" ht="15" customHeight="1" s="183">
+      <c r="A83" s="91" t="inlineStr">
         <is>
           <t>-Debiti a BT</t>
         </is>
       </c>
-      <c r="B83" s="199">
+      <c r="B83" s="196">
         <f>Input!E38</f>
         <v/>
       </c>
-      <c r="C83" s="199">
+      <c r="C83" s="196">
         <f>Input!F38</f>
         <v/>
       </c>
-      <c r="D83" s="200">
+      <c r="D83" s="197">
         <f>IFERROR((B83-C83)/C83,"")</f>
         <v/>
       </c>
       <c r="E83" s="78" t="n"/>
       <c r="F83" s="78" t="n"/>
     </row>
-    <row r="84" ht="15" customHeight="1">
-      <c r="A84" s="96" t="inlineStr">
+    <row r="84" ht="15" customHeight="1" s="183">
+      <c r="A84" s="91" t="inlineStr">
         <is>
           <t>-Debiti a LT</t>
         </is>
       </c>
-      <c r="B84" s="199">
+      <c r="B84" s="196">
         <f>Input!E39</f>
         <v/>
       </c>
-      <c r="C84" s="199">
+      <c r="C84" s="196">
         <f>Input!F39</f>
         <v/>
       </c>
-      <c r="D84" s="200">
+      <c r="D84" s="197">
         <f>IFERROR((B84-C84)/C84,"")</f>
         <v/>
       </c>
       <c r="E84" s="78" t="n"/>
       <c r="F84" s="78" t="n"/>
     </row>
-    <row r="85" ht="15" customHeight="1">
-      <c r="A85" s="88" t="inlineStr">
+    <row r="85" ht="15" customHeight="1" s="183">
+      <c r="A85" s="86" t="inlineStr">
         <is>
           <t>% Tot. Debiti su Tot. Passivo</t>
         </is>
       </c>
-      <c r="B85" s="201">
+      <c r="B85" s="198">
         <f>B$82/B$73</f>
         <v/>
       </c>
-      <c r="C85" s="201">
+      <c r="C85" s="198">
         <f>C$82/C$73</f>
         <v/>
       </c>
-      <c r="D85" s="90" t="n"/>
+      <c r="D85" s="87" t="n"/>
       <c r="E85" s="78" t="n"/>
       <c r="F85" s="78" t="n"/>
     </row>
-    <row r="86" ht="15" customHeight="1">
-      <c r="A86" s="86" t="inlineStr">
+    <row r="86" ht="15" customHeight="1" s="183">
+      <c r="A86" s="85" t="inlineStr">
         <is>
           <t>Debiti Finanziari</t>
         </is>
       </c>
-      <c r="B86" s="199">
+      <c r="B86" s="196">
         <f>Input!B40</f>
         <v/>
       </c>
-      <c r="C86" s="199">
+      <c r="C86" s="196">
         <f>Input!C40</f>
         <v/>
       </c>
-      <c r="D86" s="200">
+      <c r="D86" s="197">
         <f>IFERROR((B86-C86)/C86,"")</f>
         <v/>
       </c>
       <c r="E86" s="78" t="n"/>
       <c r="F86" s="78" t="n"/>
     </row>
-    <row r="87" ht="15" customHeight="1">
-      <c r="A87" s="96" t="inlineStr">
+    <row r="87" ht="15" customHeight="1" s="183">
+      <c r="A87" s="91" t="inlineStr">
         <is>
           <t>-Debiti Finanziari a BT</t>
         </is>
       </c>
-      <c r="B87" s="199">
+      <c r="B87" s="196">
         <f>Input!B41</f>
         <v/>
       </c>
-      <c r="C87" s="199">
+      <c r="C87" s="196">
         <f>Input!C41</f>
         <v/>
       </c>
-      <c r="D87" s="200">
+      <c r="D87" s="197">
         <f>IFERROR((B87-C87)/C87,"")</f>
         <v/>
       </c>
       <c r="E87" s="78" t="n"/>
       <c r="F87" s="78" t="n"/>
     </row>
-    <row r="88" ht="15" customHeight="1">
-      <c r="A88" s="96" t="inlineStr">
+    <row r="88" ht="15" customHeight="1" s="183">
+      <c r="A88" s="91" t="inlineStr">
         <is>
           <t>-Debiti Finanziari a LT</t>
         </is>
       </c>
-      <c r="B88" s="199">
+      <c r="B88" s="196">
         <f>Input!B42</f>
         <v/>
       </c>
-      <c r="C88" s="199">
+      <c r="C88" s="196">
         <f>Input!C42</f>
         <v/>
       </c>
-      <c r="D88" s="200">
+      <c r="D88" s="197">
         <f>IFERROR((B88-C88)/C88,"")</f>
         <v/>
       </c>
       <c r="E88" s="78" t="n"/>
       <c r="F88" s="78" t="n"/>
     </row>
-    <row r="89" ht="15" customHeight="1">
-      <c r="A89" s="88" t="inlineStr">
+    <row r="89" ht="15" customHeight="1" s="183">
+      <c r="A89" s="86" t="inlineStr">
         <is>
           <t>% Debiti Finanz. su Tot. Passivo</t>
         </is>
       </c>
-      <c r="B89" s="201">
+      <c r="B89" s="198">
         <f>B$86/B$73</f>
         <v/>
       </c>
-      <c r="C89" s="201">
+      <c r="C89" s="198">
         <f>C$86/C$73</f>
         <v/>
       </c>
-      <c r="D89" s="85" t="n"/>
+      <c r="D89" s="84" t="n"/>
       <c r="E89" s="78" t="n"/>
       <c r="F89" s="78" t="n"/>
     </row>
-    <row r="90" ht="15" customHeight="1">
-      <c r="A90" s="96" t="inlineStr">
+    <row r="90" ht="15" customHeight="1" s="183">
+      <c r="A90" s="91" t="inlineStr">
         <is>
           <t>Ratei e Risconti Passivi</t>
         </is>
       </c>
-      <c r="B90" s="199">
+      <c r="B90" s="196">
         <f>Input!B43</f>
         <v/>
       </c>
-      <c r="C90" s="199">
+      <c r="C90" s="196">
         <f>Input!C43</f>
         <v/>
       </c>
-      <c r="D90" s="200">
+      <c r="D90" s="197">
         <f>IFERROR((B90-C90)/C90,"")</f>
         <v/>
       </c>
       <c r="E90" s="78" t="n"/>
       <c r="F90" s="78" t="n"/>
     </row>
-    <row r="91" ht="15" customHeight="1">
-      <c r="A91" s="97" t="inlineStr">
+    <row r="91" ht="15" customHeight="1" s="183">
+      <c r="A91" s="92" t="inlineStr">
         <is>
           <t>% Ratei e Risconti Passivi su Tot. Passivo</t>
         </is>
       </c>
-      <c r="B91" s="206">
+      <c r="B91" s="203">
         <f>B$90/B$73</f>
         <v/>
       </c>
-      <c r="C91" s="206">
+      <c r="C91" s="203">
         <f>C$90/C$73</f>
         <v/>
       </c>
-      <c r="D91" s="99" t="n"/>
+      <c r="D91" s="93" t="n"/>
       <c r="E91" s="78" t="n"/>
       <c r="F91" s="78" t="n"/>
     </row>
-    <row r="92" ht="9" customHeight="1">
-      <c r="A92" s="100" t="n"/>
+    <row r="92" ht="9" customHeight="1" s="183">
+      <c r="A92" s="94" t="n"/>
       <c r="B92" s="80" t="n"/>
       <c r="C92" s="80" t="n"/>
       <c r="D92" s="80" t="n"/>
       <c r="E92" s="78" t="n"/>
       <c r="F92" s="78" t="n"/>
     </row>
-    <row r="93" ht="3" customHeight="1">
-      <c r="A93" s="101" t="n"/>
+    <row r="93" ht="3" customHeight="1" s="183">
+      <c r="A93" s="95" t="n"/>
       <c r="B93" s="80" t="n"/>
       <c r="C93" s="80" t="n"/>
       <c r="D93" s="80" t="n"/>
       <c r="E93" s="78" t="n"/>
       <c r="F93" s="78" t="n"/>
     </row>
-    <row r="94" ht="6.75" customHeight="1">
-      <c r="A94" s="102" t="n"/>
-      <c r="B94" s="103" t="n"/>
-      <c r="C94" s="103" t="n"/>
+    <row r="94" ht="6.75" customHeight="1" s="183">
+      <c r="A94" s="96" t="n"/>
+      <c r="B94" s="97" t="n"/>
+      <c r="C94" s="97" t="n"/>
       <c r="D94" s="80" t="n"/>
       <c r="E94" s="78" t="n"/>
       <c r="F94" s="78" t="n"/>
     </row>
-    <row r="95" ht="17.45" customHeight="1">
-      <c r="A95" s="120" t="inlineStr">
+    <row r="95" ht="17.45" customHeight="1" s="183">
+      <c r="A95" s="107" t="inlineStr">
         <is>
           <t>CONTO ECONOMICO</t>
         </is>
       </c>
-      <c r="B95" s="121" t="n"/>
-      <c r="C95" s="121" t="n"/>
-      <c r="D95" s="119" t="n"/>
+      <c r="B95" s="108" t="n"/>
+      <c r="C95" s="108" t="n"/>
+      <c r="D95" s="106" t="n"/>
       <c r="E95" s="78" t="n"/>
       <c r="F95" s="78" t="n"/>
     </row>
-    <row r="96" ht="17.1" customHeight="1">
-      <c r="A96" s="138" t="inlineStr">
+    <row r="96" ht="17.1" customHeight="1" s="183">
+      <c r="A96" s="122" t="inlineStr">
         <is>
           <t>Voce</t>
         </is>
       </c>
-      <c r="B96" s="142">
+      <c r="B96" s="125">
         <f>Input!$B$6</f>
         <v/>
       </c>
-      <c r="C96" s="142">
+      <c r="C96" s="125">
         <f>Input!$C$6</f>
         <v/>
       </c>
-      <c r="D96" s="142" t="inlineStr">
+      <c r="D96" s="125" t="inlineStr">
         <is>
           <t>Var %</t>
         </is>
@@ -6977,474 +6998,474 @@
       <c r="E96" s="78" t="n"/>
       <c r="F96" s="78" t="n"/>
     </row>
-    <row r="97" ht="10.35" customHeight="1">
-      <c r="A97" s="84" t="n"/>
-      <c r="B97" s="85" t="n"/>
-      <c r="C97" s="85" t="n"/>
-      <c r="D97" s="85" t="n"/>
+    <row r="97" ht="10.35" customHeight="1" s="183">
+      <c r="A97" s="83" t="n"/>
+      <c r="B97" s="84" t="n"/>
+      <c r="C97" s="84" t="n"/>
+      <c r="D97" s="84" t="n"/>
       <c r="E97" s="78" t="n"/>
       <c r="F97" s="78" t="n"/>
     </row>
-    <row r="98" ht="15" customHeight="1">
-      <c r="A98" s="86" t="inlineStr">
+    <row r="98" ht="15" customHeight="1" s="183">
+      <c r="A98" s="85" t="inlineStr">
         <is>
           <t>Valore della Produzione</t>
         </is>
       </c>
-      <c r="B98" s="199">
+      <c r="B98" s="196">
         <f>Input!B7</f>
         <v/>
       </c>
-      <c r="C98" s="199">
+      <c r="C98" s="196">
         <f>Input!C7</f>
         <v/>
       </c>
-      <c r="D98" s="200">
+      <c r="D98" s="197">
         <f>IFERROR((B98-C98)/C98,"")</f>
         <v/>
       </c>
       <c r="E98" s="78" t="n"/>
       <c r="F98" s="78" t="n"/>
     </row>
-    <row r="99" ht="15" customHeight="1">
-      <c r="A99" s="96" t="inlineStr">
+    <row r="99" ht="15" customHeight="1" s="183">
+      <c r="A99" s="91" t="inlineStr">
         <is>
           <t>-Ricavi di vendita</t>
         </is>
       </c>
-      <c r="B99" s="199">
+      <c r="B99" s="196">
         <f>Input!B8</f>
         <v/>
       </c>
-      <c r="C99" s="199">
+      <c r="C99" s="196">
         <f>Input!C8</f>
         <v/>
       </c>
-      <c r="D99" s="200">
+      <c r="D99" s="197">
         <f>IFERROR((B99-C99)/C99,"")</f>
         <v/>
       </c>
       <c r="E99" s="78" t="n"/>
       <c r="F99" s="78" t="n"/>
     </row>
-    <row r="100" ht="15" customHeight="1">
-      <c r="A100" s="86" t="inlineStr">
+    <row r="100" ht="15" customHeight="1" s="183">
+      <c r="A100" s="85" t="inlineStr">
         <is>
           <t>Costi della Produzione</t>
         </is>
       </c>
-      <c r="B100" s="199">
+      <c r="B100" s="196">
         <f>Input!B9</f>
         <v/>
       </c>
-      <c r="C100" s="199">
+      <c r="C100" s="196">
         <f>Input!C9</f>
         <v/>
       </c>
-      <c r="D100" s="200">
+      <c r="D100" s="197">
         <f>IFERROR((B100-C100)/C100,"")</f>
         <v/>
       </c>
       <c r="E100" s="78" t="n"/>
       <c r="F100" s="78" t="n"/>
     </row>
-    <row r="101" ht="15" customHeight="1">
-      <c r="A101" s="96" t="inlineStr">
+    <row r="101" ht="15" customHeight="1" s="183">
+      <c r="A101" s="91" t="inlineStr">
         <is>
           <t xml:space="preserve">-Costi per Materie </t>
         </is>
       </c>
-      <c r="B101" s="199">
+      <c r="B101" s="196">
         <f>Input!B10</f>
         <v/>
       </c>
-      <c r="C101" s="199">
+      <c r="C101" s="196">
         <f>Input!C10</f>
         <v/>
       </c>
-      <c r="D101" s="200">
+      <c r="D101" s="197">
         <f>IFERROR((B101-C101)/C101,"")</f>
         <v/>
       </c>
       <c r="E101" s="78" t="n"/>
       <c r="F101" s="78" t="n"/>
     </row>
-    <row r="102" ht="15" customHeight="1">
-      <c r="A102" s="88" t="inlineStr">
+    <row r="102" ht="15" customHeight="1" s="183">
+      <c r="A102" s="86" t="inlineStr">
         <is>
           <t>% Costi Materie su Costi prod.</t>
         </is>
       </c>
-      <c r="B102" s="207">
+      <c r="B102" s="204">
         <f>B$101/B$100</f>
         <v/>
       </c>
-      <c r="C102" s="207">
+      <c r="C102" s="204">
         <f>C$101/C$100</f>
         <v/>
       </c>
-      <c r="D102" s="105" t="n"/>
+      <c r="D102" s="98" t="n"/>
       <c r="E102" s="78" t="n"/>
       <c r="F102" s="78" t="n"/>
     </row>
-    <row r="103" ht="15" customHeight="1">
-      <c r="A103" s="96" t="inlineStr">
+    <row r="103" ht="15" customHeight="1" s="183">
+      <c r="A103" s="91" t="inlineStr">
         <is>
           <t>-Costi per Servizi</t>
         </is>
       </c>
-      <c r="B103" s="199">
+      <c r="B103" s="196">
         <f>Input!B11</f>
         <v/>
       </c>
-      <c r="C103" s="199">
+      <c r="C103" s="196">
         <f>Input!C11</f>
         <v/>
       </c>
-      <c r="D103" s="200">
+      <c r="D103" s="197">
         <f>IFERROR((B103-C103)/C103,"")</f>
         <v/>
       </c>
       <c r="E103" s="78" t="n"/>
       <c r="F103" s="78" t="n"/>
     </row>
-    <row r="104" ht="15" customHeight="1">
-      <c r="A104" s="88" t="inlineStr">
+    <row r="104" ht="15" customHeight="1" s="183">
+      <c r="A104" s="86" t="inlineStr">
         <is>
           <t>% Costi Servizi su Costi prod.</t>
         </is>
       </c>
-      <c r="B104" s="207">
+      <c r="B104" s="204">
         <f>B103/B100</f>
         <v/>
       </c>
-      <c r="C104" s="207">
+      <c r="C104" s="204">
         <f>C103/C100</f>
         <v/>
       </c>
-      <c r="D104" s="105" t="n"/>
+      <c r="D104" s="98" t="n"/>
       <c r="E104" s="78" t="n"/>
       <c r="F104" s="78" t="n"/>
     </row>
-    <row r="105" ht="15" customHeight="1">
-      <c r="A105" s="96" t="inlineStr">
+    <row r="105" ht="15" customHeight="1" s="183">
+      <c r="A105" s="91" t="inlineStr">
         <is>
           <t>-Costi per godimento beni di terzi</t>
         </is>
       </c>
-      <c r="B105" s="199">
+      <c r="B105" s="196">
         <f>Input!B12</f>
         <v/>
       </c>
-      <c r="C105" s="199">
+      <c r="C105" s="196">
         <f>Input!C12</f>
         <v/>
       </c>
-      <c r="D105" s="200">
+      <c r="D105" s="197">
         <f>IFERROR((B105-C105)/C105,"")</f>
         <v/>
       </c>
       <c r="E105" s="78" t="n"/>
       <c r="F105" s="78" t="n"/>
     </row>
-    <row r="106" ht="15" customHeight="1">
-      <c r="A106" s="88" t="inlineStr">
+    <row r="106" ht="15" customHeight="1" s="183">
+      <c r="A106" s="86" t="inlineStr">
         <is>
           <t>% Costi Servizi su Costi prod.</t>
         </is>
       </c>
-      <c r="B106" s="207">
+      <c r="B106" s="204">
         <f>B$105/B$100</f>
         <v/>
       </c>
-      <c r="C106" s="207">
+      <c r="C106" s="204">
         <f>C$105/C$100</f>
         <v/>
       </c>
-      <c r="D106" s="105" t="n"/>
+      <c r="D106" s="98" t="n"/>
       <c r="E106" s="78" t="n"/>
       <c r="F106" s="78" t="n"/>
     </row>
-    <row r="107" ht="15" customHeight="1">
-      <c r="A107" s="96" t="inlineStr">
+    <row r="107" ht="15" customHeight="1" s="183">
+      <c r="A107" s="91" t="inlineStr">
         <is>
           <t>-Costi Personale</t>
         </is>
       </c>
-      <c r="B107" s="199">
+      <c r="B107" s="196">
         <f>Input!B13</f>
         <v/>
       </c>
-      <c r="C107" s="199">
+      <c r="C107" s="196">
         <f>Input!C13</f>
         <v/>
       </c>
-      <c r="D107" s="200">
+      <c r="D107" s="197">
         <f>IFERROR((B107-C107)/C107,"")</f>
         <v/>
       </c>
       <c r="E107" s="78" t="n"/>
       <c r="F107" s="78" t="n"/>
     </row>
-    <row r="108" ht="15" customHeight="1">
-      <c r="A108" s="88" t="inlineStr">
+    <row r="108" ht="15" customHeight="1" s="183">
+      <c r="A108" s="86" t="inlineStr">
         <is>
           <t>% Costi Personale su Costi prod.</t>
         </is>
       </c>
-      <c r="B108" s="207">
+      <c r="B108" s="204">
         <f>B107/B100</f>
         <v/>
       </c>
-      <c r="C108" s="207">
+      <c r="C108" s="204">
         <f>C107/C100</f>
         <v/>
       </c>
-      <c r="D108" s="105" t="n"/>
+      <c r="D108" s="98" t="n"/>
       <c r="E108" s="78" t="n"/>
       <c r="F108" s="78" t="n"/>
     </row>
-    <row r="109" ht="15" customHeight="1">
-      <c r="A109" s="96" t="inlineStr">
+    <row r="109" ht="15" customHeight="1" s="183">
+      <c r="A109" s="91" t="inlineStr">
         <is>
           <t>-Ammortamenti</t>
         </is>
       </c>
-      <c r="B109" s="199">
+      <c r="B109" s="196">
         <f>Input!B14</f>
         <v/>
       </c>
-      <c r="C109" s="199">
+      <c r="C109" s="196">
         <f>Input!C14</f>
         <v/>
       </c>
-      <c r="D109" s="200">
+      <c r="D109" s="197">
         <f>IFERROR((B109-C109)/C109,"")</f>
         <v/>
       </c>
       <c r="E109" s="78" t="n"/>
       <c r="F109" s="78" t="n"/>
     </row>
-    <row r="110" ht="15" customHeight="1">
-      <c r="A110" s="88" t="inlineStr">
+    <row r="110" ht="15" customHeight="1" s="183">
+      <c r="A110" s="86" t="inlineStr">
         <is>
           <t>% Ammortamenti su Costi prod.</t>
         </is>
       </c>
-      <c r="B110" s="207">
+      <c r="B110" s="204">
         <f>B$109/B$100</f>
         <v/>
       </c>
-      <c r="C110" s="207">
+      <c r="C110" s="204">
         <f>C$109/C$100</f>
         <v/>
       </c>
-      <c r="D110" s="105" t="n"/>
+      <c r="D110" s="98" t="n"/>
       <c r="E110" s="78" t="n"/>
       <c r="F110" s="78" t="n"/>
     </row>
-    <row r="111" ht="15" customHeight="1">
-      <c r="A111" s="96" t="inlineStr">
+    <row r="111" ht="15" customHeight="1" s="183">
+      <c r="A111" s="91" t="inlineStr">
         <is>
           <t>-Accantonamenti per rischi</t>
         </is>
       </c>
-      <c r="B111" s="199">
+      <c r="B111" s="196">
         <f>Input!B15</f>
         <v/>
       </c>
-      <c r="C111" s="199">
+      <c r="C111" s="196">
         <f>Input!C15</f>
         <v/>
       </c>
-      <c r="D111" s="200">
+      <c r="D111" s="197">
         <f>IFERROR((B111-C111)/C111,"")</f>
         <v/>
       </c>
       <c r="E111" s="78" t="n"/>
       <c r="F111" s="78" t="n"/>
     </row>
-    <row r="112" ht="15" customHeight="1">
-      <c r="A112" s="88" t="inlineStr">
+    <row r="112" ht="15" customHeight="1" s="183">
+      <c r="A112" s="86" t="inlineStr">
         <is>
           <t>% Accantonamenti per rischi su Costi prod.</t>
         </is>
       </c>
-      <c r="B112" s="207">
+      <c r="B112" s="204">
         <f>$B$111/$B$100</f>
         <v/>
       </c>
-      <c r="C112" s="207">
+      <c r="C112" s="204">
         <f>$B$111/$B$100</f>
         <v/>
       </c>
-      <c r="D112" s="105" t="n"/>
+      <c r="D112" s="98" t="n"/>
       <c r="E112" s="78" t="n"/>
       <c r="F112" s="78" t="n"/>
     </row>
-    <row r="113" ht="15" customHeight="1">
-      <c r="A113" s="96" t="inlineStr">
+    <row r="113" ht="15" customHeight="1" s="183">
+      <c r="A113" s="91" t="inlineStr">
         <is>
           <t>-Oneri diversi di gestione</t>
         </is>
       </c>
-      <c r="B113" s="199">
+      <c r="B113" s="196">
         <f>Input!B16</f>
         <v/>
       </c>
-      <c r="C113" s="199">
+      <c r="C113" s="196">
         <f>Input!C16</f>
         <v/>
       </c>
-      <c r="D113" s="200">
+      <c r="D113" s="197">
         <f>IFERROR((B113-C113)/C113,"")</f>
         <v/>
       </c>
       <c r="E113" s="78" t="n"/>
       <c r="F113" s="78" t="n"/>
     </row>
-    <row r="114" ht="15.95" customHeight="1" thickBot="1">
-      <c r="A114" s="91" t="inlineStr">
+    <row r="114" ht="15.95" customHeight="1" s="183" thickBot="1">
+      <c r="A114" s="88" t="inlineStr">
         <is>
           <t>% Oneri diversi di gestione su Costi prod.</t>
         </is>
       </c>
-      <c r="B114" s="208">
+      <c r="B114" s="205">
         <f>B$113/B$100</f>
         <v/>
       </c>
-      <c r="C114" s="208">
+      <c r="C114" s="205">
         <f>C$113/C$100</f>
         <v/>
       </c>
-      <c r="D114" s="107" t="n"/>
+      <c r="D114" s="99" t="n"/>
       <c r="E114" s="78" t="n"/>
       <c r="F114" s="78" t="n"/>
     </row>
-    <row r="115" ht="18" customHeight="1" thickTop="1">
-      <c r="A115" s="86" t="inlineStr">
+    <row r="115" ht="18" customHeight="1" s="183" thickTop="1">
+      <c r="A115" s="85" t="inlineStr">
         <is>
           <t>EBIT</t>
         </is>
       </c>
-      <c r="B115" s="203">
+      <c r="B115" s="200">
         <f>Input!B17</f>
         <v/>
       </c>
-      <c r="C115" s="203">
+      <c r="C115" s="200">
         <f>Input!C17</f>
         <v/>
       </c>
-      <c r="D115" s="200">
+      <c r="D115" s="197">
         <f>IFERROR((B115-C115)/C115,"")</f>
         <v/>
       </c>
       <c r="E115" s="78" t="n"/>
       <c r="F115" s="78" t="n"/>
     </row>
-    <row r="116" ht="15" customHeight="1">
-      <c r="A116" s="88" t="inlineStr">
+    <row r="116" ht="15" customHeight="1" s="183">
+      <c r="A116" s="86" t="inlineStr">
         <is>
           <t>% EBIT su Valore Produzione</t>
         </is>
       </c>
-      <c r="B116" s="207">
+      <c r="B116" s="204">
         <f>B$115/B$98</f>
         <v/>
       </c>
-      <c r="C116" s="207">
+      <c r="C116" s="204">
         <f>C$115/C$98</f>
         <v/>
       </c>
-      <c r="D116" s="85" t="n"/>
+      <c r="D116" s="84" t="n"/>
       <c r="E116" s="78" t="n"/>
       <c r="F116" s="78" t="n"/>
     </row>
-    <row r="117" ht="15" customHeight="1">
-      <c r="A117" s="86" t="inlineStr">
+    <row r="117" ht="15" customHeight="1" s="183">
+      <c r="A117" s="85" t="inlineStr">
         <is>
           <t>Proventi Finanziari</t>
         </is>
       </c>
-      <c r="B117" s="199">
+      <c r="B117" s="196">
         <f>Input!B18</f>
         <v/>
       </c>
-      <c r="C117" s="199">
+      <c r="C117" s="196">
         <f>Input!C18</f>
         <v/>
       </c>
-      <c r="D117" s="200">
+      <c r="D117" s="197">
         <f>IFERROR((B117-C117)/C117,"")</f>
         <v/>
       </c>
       <c r="E117" s="78" t="n"/>
       <c r="F117" s="78" t="n"/>
     </row>
-    <row r="118" ht="15.95" customHeight="1" thickBot="1">
-      <c r="A118" s="86" t="inlineStr">
+    <row r="118" ht="15.95" customHeight="1" s="183" thickBot="1">
+      <c r="A118" s="85" t="inlineStr">
         <is>
           <t>Oneri Finanziari</t>
         </is>
       </c>
-      <c r="B118" s="209">
+      <c r="B118" s="206">
         <f>Input!B19</f>
         <v/>
       </c>
-      <c r="C118" s="209">
+      <c r="C118" s="206">
         <f>Input!C19</f>
         <v/>
       </c>
-      <c r="D118" s="210">
+      <c r="D118" s="207">
         <f>IFERROR((B118-C118)/C118,"")</f>
         <v/>
       </c>
       <c r="E118" s="78" t="n"/>
       <c r="F118" s="78" t="n"/>
     </row>
-    <row r="119" ht="15.95" customHeight="1" thickTop="1">
-      <c r="A119" s="109" t="inlineStr">
+    <row r="119" ht="15.95" customHeight="1" s="183" thickTop="1">
+      <c r="A119" s="100" t="inlineStr">
         <is>
           <t>Utile (Perdita) dell'esercizio</t>
         </is>
       </c>
-      <c r="B119" s="211">
+      <c r="B119" s="208">
         <f>Input!B20</f>
         <v/>
       </c>
-      <c r="C119" s="211">
+      <c r="C119" s="208">
         <f>Input!C20</f>
         <v/>
       </c>
-      <c r="D119" s="212">
+      <c r="D119" s="209">
         <f>IFERROR((B119-C119)/C119,"")</f>
         <v/>
       </c>
       <c r="E119" s="78" t="n"/>
       <c r="F119" s="78" t="n"/>
     </row>
-    <row r="120" ht="13.35" customHeight="1">
-      <c r="A120" s="163" t="inlineStr">
+    <row r="120" ht="13.35" customHeight="1" s="183">
+      <c r="A120" s="137" t="inlineStr">
         <is>
           <t>Dipendenti</t>
         </is>
       </c>
-      <c r="B120" s="213">
+      <c r="B120" s="168">
         <f>Input!B21</f>
         <v/>
       </c>
-      <c r="C120" s="213">
+      <c r="C120" s="168">
         <f>Input!C21</f>
         <v/>
       </c>
-      <c r="D120" s="214">
+      <c r="D120" s="210">
         <f>IFERROR((B120-C120)/C120,"")</f>
         <v/>
       </c>
       <c r="E120" s="78" t="n"/>
       <c r="F120" s="78" t="n"/>
     </row>
-    <row r="121" ht="9" customHeight="1">
+    <row r="121" ht="9" customHeight="1" s="183">
       <c r="A121" s="78" t="n"/>
       <c r="B121" s="78" t="n"/>
       <c r="C121" s="78" t="n"/>
@@ -7452,7 +7473,7 @@
       <c r="E121" s="78" t="n"/>
       <c r="F121" s="78" t="n"/>
     </row>
-    <row r="122" ht="8.25" customHeight="1" thickBot="1">
+    <row r="122" ht="8.25" customHeight="1" s="183" thickBot="1">
       <c r="A122" s="78" t="n"/>
       <c r="B122" s="78" t="n"/>
       <c r="C122" s="78" t="n"/>
@@ -7460,448 +7481,448 @@
       <c r="E122" s="78" t="n"/>
       <c r="F122" s="78" t="n"/>
     </row>
-    <row r="123" ht="15" customHeight="1">
-      <c r="A123" s="153" t="inlineStr">
+    <row r="123" ht="15" customHeight="1" s="183">
+      <c r="A123" s="129" t="inlineStr">
         <is>
           <t>INDICI</t>
         </is>
       </c>
-      <c r="B123" s="122">
+      <c r="B123" s="109">
         <f>$B$96</f>
         <v/>
       </c>
-      <c r="C123" s="147">
+      <c r="C123" s="128">
         <f>$C$96</f>
         <v/>
       </c>
-      <c r="D123" s="122" t="n"/>
+      <c r="D123" s="109" t="n"/>
       <c r="E123" s="78" t="n"/>
       <c r="F123" s="78" t="n"/>
     </row>
-    <row r="124" ht="11.45" customHeight="1">
-      <c r="A124" s="85" t="n"/>
-      <c r="B124" s="85" t="n"/>
-      <c r="C124" s="111" t="n"/>
-      <c r="D124" s="85" t="n"/>
+    <row r="124" ht="11.45" customHeight="1" s="183">
+      <c r="A124" s="84" t="n"/>
+      <c r="B124" s="84" t="n"/>
+      <c r="C124" s="101" t="n"/>
+      <c r="D124" s="84" t="n"/>
       <c r="E124" s="78" t="n"/>
       <c r="F124" s="78" t="n"/>
     </row>
-    <row r="125" ht="15" customHeight="1">
-      <c r="A125" s="154" t="inlineStr">
+    <row r="125" ht="15" customHeight="1" s="183">
+      <c r="A125" s="130" t="inlineStr">
         <is>
           <t>Liquidità</t>
         </is>
       </c>
-      <c r="B125" s="157" t="n"/>
-      <c r="C125" s="143" t="n"/>
-      <c r="D125" s="159" t="n"/>
+      <c r="B125" s="133" t="n"/>
+      <c r="C125" s="126" t="n"/>
+      <c r="D125" s="135" t="n"/>
       <c r="E125" s="78" t="n"/>
       <c r="F125" s="78" t="n"/>
     </row>
-    <row r="126" ht="15" customHeight="1">
-      <c r="A126" s="155" t="inlineStr">
+    <row r="126" ht="15" customHeight="1" s="183">
+      <c r="A126" s="131" t="inlineStr">
         <is>
           <t xml:space="preserve">Test Acido </t>
         </is>
       </c>
-      <c r="B126" s="215">
+      <c r="B126" s="211">
         <f>(B65+B69+B71)/(B83+B87)</f>
         <v/>
       </c>
-      <c r="C126" s="216">
+      <c r="C126" s="212">
         <f>(C65+C69+C71)/(C83+C87)</f>
         <v/>
       </c>
-      <c r="D126" s="217">
-        <f>+B126-C126</f>
+      <c r="D126" s="223">
+        <f>IF(B126-C126&lt;0,"▼",IF(B126-C126&lt;0.000001,"►","▲"))</f>
         <v/>
       </c>
       <c r="E126" s="78" t="n"/>
       <c r="F126" s="78" t="n"/>
     </row>
-    <row r="127" ht="15" customHeight="1">
-      <c r="A127" s="155" t="inlineStr">
+    <row r="127" ht="15" customHeight="1" s="183">
+      <c r="A127" s="131" t="inlineStr">
         <is>
           <t>Current Ratio</t>
         </is>
       </c>
-      <c r="B127" s="215">
+      <c r="B127" s="211">
         <f>(B63+B65+B69+B71)/(B83+B87)</f>
         <v/>
       </c>
-      <c r="C127" s="216">
+      <c r="C127" s="212">
         <f>(C63+C65+C69+C71)/(C83+C87)</f>
         <v/>
       </c>
-      <c r="D127" s="217">
-        <f>+B127-C127</f>
+      <c r="D127" s="223">
+        <f>IF(B127-C127&lt;0,"▼",IF(B127-C127&lt;0.000001,"►","▲"))</f>
         <v/>
       </c>
       <c r="E127" s="78" t="n"/>
       <c r="F127" s="78" t="n"/>
     </row>
-    <row r="128" ht="15" customHeight="1">
-      <c r="A128" s="154" t="inlineStr">
+    <row r="128" ht="15" customHeight="1" s="183">
+      <c r="A128" s="130" t="inlineStr">
         <is>
           <t>Indeb. e sostenibilità del debito</t>
         </is>
       </c>
-      <c r="B128" s="158" t="n"/>
-      <c r="C128" s="144" t="n"/>
-      <c r="D128" s="159" t="n"/>
+      <c r="B128" s="134" t="n"/>
+      <c r="C128" s="127" t="n"/>
+      <c r="D128" s="135" t="n"/>
       <c r="E128" s="78" t="n"/>
       <c r="F128" s="78" t="n"/>
     </row>
-    <row r="129" ht="15" customHeight="1">
-      <c r="A129" s="155" t="inlineStr">
+    <row r="129" ht="15" customHeight="1" s="183">
+      <c r="A129" s="131" t="inlineStr">
         <is>
           <t>Rapporto Indebitamento</t>
         </is>
       </c>
-      <c r="B129" s="215">
+      <c r="B129" s="211">
         <f>IF(B86=0,B82/B76,B86/B76)</f>
         <v/>
       </c>
-      <c r="C129" s="216">
+      <c r="C129" s="212">
         <f>IF(C86=0,C82/C76,C86/C76)</f>
         <v/>
       </c>
-      <c r="D129" s="217">
-        <f>+B129-C129</f>
+      <c r="D129" s="223">
+        <f>IF(C129-B129&lt;0,"▼",IF(C129-B129&lt;0.000001,"►","▲"))</f>
         <v/>
       </c>
       <c r="E129" s="78" t="n"/>
       <c r="F129" s="78" t="n"/>
     </row>
-    <row r="130" ht="15" customHeight="1">
-      <c r="A130" s="155" t="inlineStr">
+    <row r="130" ht="15" customHeight="1" s="183">
+      <c r="A130" s="131" t="inlineStr">
         <is>
           <t>PFN</t>
         </is>
       </c>
-      <c r="B130" s="218">
+      <c r="B130" s="214">
         <f>IF(B86=0,"Non Calcolabile",B69+B67-B86)</f>
         <v/>
       </c>
-      <c r="C130" s="219">
+      <c r="C130" s="215">
         <f>IF(C86=0,"Non Calcolabile",C69+C67-C86)</f>
         <v/>
       </c>
-      <c r="D130" s="217">
-        <f>+B130-C130</f>
+      <c r="D130" s="223">
+        <f>IF(B130-C130&lt;0,"▼",IF(B130-C130&lt;0.000001,"►","▲"))</f>
         <v/>
       </c>
       <c r="E130" s="78" t="n"/>
       <c r="F130" s="78" t="n"/>
     </row>
-    <row r="131" ht="15" customHeight="1">
-      <c r="A131" s="155" t="inlineStr">
+    <row r="131" ht="15" customHeight="1" s="183">
+      <c r="A131" s="131" t="inlineStr">
         <is>
           <t>PFN/EBITDA</t>
         </is>
       </c>
-      <c r="B131" s="215">
+      <c r="B131" s="211">
         <f>IF(B130="Non Calcolabile","Non Calcolabile",B130/B136)</f>
         <v/>
       </c>
-      <c r="C131" s="216">
+      <c r="C131" s="212">
         <f>IF(C130="Non Calcolabile","Non Calcolabile",C130/C136)</f>
         <v/>
       </c>
-      <c r="D131" s="85" t="n"/>
+      <c r="D131" s="84" t="n"/>
       <c r="E131" s="78" t="n"/>
       <c r="F131" s="78" t="n"/>
     </row>
-    <row r="132" ht="15" customHeight="1">
-      <c r="A132" s="154" t="inlineStr">
+    <row r="132" ht="15" customHeight="1" s="183">
+      <c r="A132" s="130" t="inlineStr">
         <is>
           <t>Redditività</t>
         </is>
       </c>
-      <c r="B132" s="158" t="n"/>
-      <c r="C132" s="144" t="n"/>
-      <c r="D132" s="159" t="n"/>
+      <c r="B132" s="134" t="n"/>
+      <c r="C132" s="127" t="n"/>
+      <c r="D132" s="135" t="n"/>
       <c r="E132" s="78" t="n"/>
       <c r="F132" s="78" t="n"/>
     </row>
-    <row r="133" ht="15" customHeight="1">
-      <c r="A133" s="155" t="inlineStr">
+    <row r="133" ht="15" customHeight="1" s="183">
+      <c r="A133" s="131" t="inlineStr">
         <is>
           <t>ROS</t>
         </is>
       </c>
-      <c r="B133" s="220">
+      <c r="B133" s="216">
         <f>B115/B99</f>
         <v/>
       </c>
-      <c r="C133" s="221">
+      <c r="C133" s="217">
         <f>C115/C99</f>
         <v/>
       </c>
-      <c r="D133" s="217">
-        <f>+B133-C133</f>
+      <c r="D133" s="223">
+        <f>IF(B133-C133&lt;0,"▼",IF(B133-C133&lt;0.000001,"►","▲"))</f>
         <v/>
       </c>
       <c r="E133" s="78" t="n"/>
       <c r="F133" s="78" t="n"/>
     </row>
-    <row r="134" ht="15" customHeight="1">
-      <c r="A134" s="155" t="inlineStr">
+    <row r="134" ht="15" customHeight="1" s="183">
+      <c r="A134" s="131" t="inlineStr">
         <is>
           <t>ROE</t>
         </is>
       </c>
-      <c r="B134" s="220">
+      <c r="B134" s="216">
         <f>B119/B76</f>
         <v/>
       </c>
-      <c r="C134" s="221">
+      <c r="C134" s="217">
         <f>C119/C76</f>
         <v/>
       </c>
-      <c r="D134" s="217">
-        <f>+B134-C134</f>
+      <c r="D134" s="223">
+        <f>IF(B134-C134&lt;0,"▼",IF(B134-C134&lt;0.000001,"►","▲"))</f>
         <v/>
       </c>
       <c r="E134" s="78" t="n"/>
       <c r="F134" s="78" t="n"/>
     </row>
-    <row r="135" ht="15" customHeight="1">
-      <c r="A135" s="155" t="inlineStr">
+    <row r="135" ht="15" customHeight="1" s="183">
+      <c r="A135" s="131" t="inlineStr">
         <is>
           <t>ROI</t>
         </is>
       </c>
-      <c r="B135" s="220">
+      <c r="B135" s="216">
         <f>B115/B73</f>
         <v/>
       </c>
-      <c r="C135" s="221">
+      <c r="C135" s="217">
         <f>C115/C73</f>
         <v/>
       </c>
-      <c r="D135" s="217">
-        <f>+B135-C135</f>
+      <c r="D135" s="223">
+        <f>IF(B135-C135&lt;0,"▼",IF(B135-C135&lt;0.000001,"►","▲"))</f>
         <v/>
       </c>
       <c r="E135" s="78" t="n"/>
       <c r="F135" s="78" t="n"/>
     </row>
-    <row r="136" ht="15" customHeight="1">
-      <c r="A136" s="155" t="inlineStr">
+    <row r="136" ht="15" customHeight="1" s="183">
+      <c r="A136" s="131" t="inlineStr">
         <is>
           <t>EBITDA</t>
         </is>
       </c>
-      <c r="B136" s="218">
+      <c r="B136" s="214">
         <f>B115+B109</f>
         <v/>
       </c>
-      <c r="C136" s="219">
+      <c r="C136" s="215">
         <f>C115+C109</f>
         <v/>
       </c>
-      <c r="D136" s="217">
-        <f>+B136-C136</f>
+      <c r="D136" s="223">
+        <f>IF(B136-C136&lt;0,"▼",IF(B136-C136&lt;0.000001,"►","▲"))</f>
         <v/>
       </c>
       <c r="E136" s="78" t="n"/>
       <c r="F136" s="78" t="n"/>
     </row>
-    <row r="137" ht="15" customHeight="1">
-      <c r="A137" s="154" t="inlineStr">
+    <row r="137" ht="15" customHeight="1" s="183">
+      <c r="A137" s="130" t="inlineStr">
         <is>
           <t>Efficienza</t>
         </is>
       </c>
-      <c r="B137" s="158" t="n"/>
-      <c r="C137" s="144" t="n"/>
-      <c r="D137" s="159" t="n"/>
+      <c r="B137" s="134" t="n"/>
+      <c r="C137" s="127" t="n"/>
+      <c r="D137" s="135" t="n"/>
       <c r="E137" s="78" t="n"/>
       <c r="F137" s="78" t="n"/>
     </row>
-    <row r="138" ht="15" customHeight="1">
-      <c r="A138" s="155" t="inlineStr">
+    <row r="138" ht="15" customHeight="1" s="183">
+      <c r="A138" s="131" t="inlineStr">
         <is>
           <t>Asset Turnover (AT)</t>
         </is>
       </c>
-      <c r="B138" s="215">
+      <c r="B138" s="211">
         <f>B99/B73</f>
         <v/>
       </c>
-      <c r="C138" s="216">
+      <c r="C138" s="212">
         <f>C99/C73</f>
         <v/>
       </c>
-      <c r="D138" s="217">
-        <f>+B138-C138</f>
+      <c r="D138" s="223">
+        <f>IF(B138-C138&lt;0,"▼",IF(B138-C138&lt;0.000001,"►","▲"))</f>
         <v/>
       </c>
       <c r="E138" s="78" t="n"/>
       <c r="F138" s="78" t="n"/>
     </row>
-    <row r="139" ht="15" customHeight="1">
-      <c r="A139" s="155" t="inlineStr">
+    <row r="139" ht="15" customHeight="1" s="183">
+      <c r="A139" s="131" t="inlineStr">
         <is>
           <t>DSO</t>
         </is>
       </c>
-      <c r="B139" s="222">
+      <c r="B139" s="218">
         <f>IF(Input!B45="n.d.","Non Calcolabile",Input!B45/Report!B98*365)</f>
         <v/>
       </c>
-      <c r="C139" s="223">
+      <c r="C139" s="219">
         <f>IF(Input!C45="n.d.","Non Calcolabile",Input!C45/Report!C98*365)</f>
         <v/>
       </c>
-      <c r="D139" s="217">
-        <f>+B139-C139</f>
+      <c r="D139" s="223">
+        <f>IF(C139-B139&lt;0,"▼",IF(C139-B139&lt;0.000001,"►","▲"))</f>
         <v/>
       </c>
       <c r="E139" s="78" t="n"/>
       <c r="F139" s="78" t="n"/>
     </row>
-    <row r="140" ht="15" customHeight="1">
-      <c r="A140" s="155" t="inlineStr">
+    <row r="140" ht="15" customHeight="1" s="183">
+      <c r="A140" s="131" t="inlineStr">
         <is>
           <t>DPO</t>
         </is>
       </c>
-      <c r="B140" s="222">
+      <c r="B140" s="218">
         <f>IF(Input!B44="n.d.","Non Calcolabile",Input!B44/Report!B100*365)</f>
         <v/>
       </c>
-      <c r="C140" s="223">
+      <c r="C140" s="219">
         <f>IF(Input!C44="n.d.","Non Calcolabile",Input!C44/Report!C100*365)</f>
         <v/>
       </c>
-      <c r="D140" s="217">
-        <f>+B140-C140</f>
+      <c r="D140" s="223">
+        <f>IF(B140-C140&lt;0,"▼",IF(B140-C140&lt;0.000001,"►","▲"))</f>
         <v/>
       </c>
       <c r="E140" s="78" t="n"/>
       <c r="F140" s="78" t="n"/>
     </row>
-    <row r="141" ht="16.35" customHeight="1">
-      <c r="A141" s="155" t="inlineStr">
+    <row r="141" ht="16.35" customHeight="1" s="183">
+      <c r="A141" s="131" t="inlineStr">
         <is>
           <t>DIO</t>
         </is>
       </c>
-      <c r="B141" s="222">
+      <c r="B141" s="218">
         <f>B63/B100*365</f>
         <v/>
       </c>
-      <c r="C141" s="223">
+      <c r="C141" s="219">
         <f>C63/C100*365</f>
         <v/>
       </c>
-      <c r="D141" s="217">
-        <f>+B141-C141</f>
+      <c r="D141" s="223">
+        <f>IF(C141-B141&lt;0,"▼",IF(C141-B141&lt;0.000001,"►","▲"))</f>
         <v/>
       </c>
       <c r="E141" s="78" t="n"/>
       <c r="F141" s="78" t="n"/>
     </row>
-    <row r="142" ht="15.95" customHeight="1" thickBot="1">
-      <c r="A142" s="156" t="inlineStr">
+    <row r="142" ht="15.95" customHeight="1" s="183" thickBot="1">
+      <c r="A142" s="132" t="inlineStr">
         <is>
           <t>CCC</t>
         </is>
       </c>
-      <c r="B142" s="224">
+      <c r="B142" s="220">
         <f>IF(OR(B139="Non Calcolabile",B140="Non Calcolabile"),"Non Calcolabile",B139+B141-B140)</f>
         <v/>
       </c>
-      <c r="C142" s="225">
+      <c r="C142" s="221">
         <f>IF(OR(C139="Non Calcolabile",C140="Non Calcolabile"),"Non Calcolabile",C139+C141-C140)</f>
         <v/>
       </c>
-      <c r="D142" s="226">
-        <f>+B142-C142</f>
+      <c r="D142" s="224">
+        <f>IF(C142-B142&lt;0,"▼",IF(C142-B142&lt;0.000001,"►","▲"))</f>
         <v/>
       </c>
       <c r="E142" s="78" t="n"/>
       <c r="F142" s="78" t="n"/>
     </row>
-    <row r="143" ht="15" customHeight="1">
+    <row r="143" ht="15" customHeight="1" s="183">
       <c r="E143" s="78" t="n"/>
       <c r="F143" s="78" t="n"/>
     </row>
-    <row r="144" ht="15" customHeight="1">
+    <row r="144" ht="15" customHeight="1" s="183">
       <c r="E144" s="78" t="n"/>
       <c r="F144" s="78" t="n"/>
     </row>
-    <row r="145" ht="15" customHeight="1">
+    <row r="145" ht="15" customHeight="1" s="183">
       <c r="E145" s="78" t="n"/>
       <c r="F145" s="78" t="n"/>
     </row>
-    <row r="146" ht="15" customHeight="1">
+    <row r="146" ht="15" customHeight="1" s="183">
       <c r="E146" s="78" t="n"/>
       <c r="F146" s="78" t="n"/>
     </row>
-    <row r="147" ht="15" customHeight="1">
+    <row r="147" ht="15" customHeight="1" s="183">
       <c r="E147" s="78" t="n"/>
       <c r="F147" s="78" t="n"/>
     </row>
-    <row r="148" ht="15" customHeight="1">
+    <row r="148" ht="15" customHeight="1" s="183">
       <c r="E148" s="78" t="n"/>
       <c r="F148" s="78" t="n"/>
     </row>
-    <row r="149" ht="15" customHeight="1">
+    <row r="149" ht="15" customHeight="1" s="183">
       <c r="E149" s="78" t="n"/>
       <c r="F149" s="78" t="n"/>
     </row>
-    <row r="150" ht="15" customHeight="1">
+    <row r="150" ht="15" customHeight="1" s="183">
       <c r="E150" s="78" t="n"/>
       <c r="F150" s="78" t="n"/>
     </row>
-    <row r="151" ht="15" customHeight="1">
+    <row r="151" ht="15" customHeight="1" s="183">
       <c r="E151" s="78" t="n"/>
       <c r="F151" s="78" t="n"/>
     </row>
-    <row r="152" ht="15" customHeight="1">
+    <row r="152" ht="15" customHeight="1" s="183">
       <c r="E152" s="78" t="n"/>
       <c r="F152" s="78" t="n"/>
     </row>
-    <row r="153" ht="15" customHeight="1">
+    <row r="153" ht="15" customHeight="1" s="183">
       <c r="E153" s="78" t="n"/>
       <c r="F153" s="78" t="n"/>
     </row>
-    <row r="154" ht="15" customHeight="1">
+    <row r="154" ht="15" customHeight="1" s="183">
       <c r="E154" s="78" t="n"/>
       <c r="F154" s="78" t="n"/>
     </row>
-    <row r="155" ht="15" customHeight="1">
+    <row r="155" ht="15" customHeight="1" s="183">
       <c r="E155" s="78" t="n"/>
       <c r="F155" s="78" t="n"/>
     </row>
-    <row r="156" ht="15" customHeight="1">
+    <row r="156" ht="15" customHeight="1" s="183">
       <c r="E156" s="78" t="n"/>
       <c r="F156" s="78" t="n"/>
     </row>
-    <row r="157" ht="15" customHeight="1">
+    <row r="157" ht="15" customHeight="1" s="183">
       <c r="E157" s="78" t="n"/>
       <c r="F157" s="78" t="n"/>
     </row>
-    <row r="158" ht="15" customHeight="1">
+    <row r="158" ht="15" customHeight="1" s="183">
       <c r="E158" s="78" t="n"/>
       <c r="F158" s="78" t="n"/>
     </row>
-    <row r="159" ht="15" customHeight="1">
+    <row r="159" ht="15" customHeight="1" s="183">
       <c r="E159" s="78" t="n"/>
       <c r="F159" s="78" t="n"/>
     </row>
-    <row r="160" ht="15" customHeight="1">
+    <row r="160" ht="15" customHeight="1" s="183">
       <c r="E160" s="78" t="n"/>
       <c r="F160" s="78" t="n"/>
     </row>
-    <row r="161" ht="15" customHeight="1">
+    <row r="161" ht="15" customHeight="1" s="183">
       <c r="E161" s="78" t="n"/>
       <c r="F161" s="78" t="n"/>
     </row>
-    <row r="162" ht="15" customHeight="1">
+    <row r="162" ht="15" customHeight="1" s="183">
       <c r="A162" s="78" t="n"/>
       <c r="B162" s="78" t="n"/>
       <c r="C162" s="78" t="n"/>
@@ -7909,7 +7930,7 @@
       <c r="E162" s="78" t="n"/>
       <c r="F162" s="78" t="n"/>
     </row>
-    <row r="163" ht="15" customHeight="1">
+    <row r="163" ht="15" customHeight="1" s="183">
       <c r="A163" s="78" t="n"/>
       <c r="B163" s="78" t="n"/>
       <c r="C163" s="78" t="n"/>
@@ -7917,7 +7938,7 @@
       <c r="E163" s="78" t="n"/>
       <c r="F163" s="78" t="n"/>
     </row>
-    <row r="164" ht="15" customHeight="1">
+    <row r="164" ht="15" customHeight="1" s="183">
       <c r="A164" s="78" t="n"/>
       <c r="B164" s="78" t="n"/>
       <c r="C164" s="78" t="n"/>
@@ -7925,7 +7946,7 @@
       <c r="E164" s="78" t="n"/>
       <c r="F164" s="78" t="n"/>
     </row>
-    <row r="165" ht="15" customHeight="1">
+    <row r="165" ht="15" customHeight="1" s="183">
       <c r="A165" s="78" t="n"/>
       <c r="B165" s="78" t="n"/>
       <c r="C165" s="78" t="n"/>
@@ -7933,7 +7954,7 @@
       <c r="E165" s="78" t="n"/>
       <c r="F165" s="78" t="n"/>
     </row>
-    <row r="166" ht="15" customHeight="1">
+    <row r="166" ht="15" customHeight="1" s="183">
       <c r="A166" s="78" t="n"/>
       <c r="B166" s="78" t="n"/>
       <c r="C166" s="78" t="n"/>
@@ -7941,7 +7962,7 @@
       <c r="E166" s="78" t="n"/>
       <c r="F166" s="78" t="n"/>
     </row>
-    <row r="167" ht="15" customHeight="1">
+    <row r="167" ht="15" customHeight="1" s="183">
       <c r="A167" s="78" t="n"/>
       <c r="B167" s="78" t="n"/>
       <c r="C167" s="78" t="n"/>
@@ -7949,7 +7970,7 @@
       <c r="E167" s="78" t="n"/>
       <c r="F167" s="78" t="n"/>
     </row>
-    <row r="168" ht="15" customHeight="1">
+    <row r="168" ht="15" customHeight="1" s="183">
       <c r="A168" s="78" t="n"/>
       <c r="B168" s="78" t="n"/>
       <c r="C168" s="78" t="n"/>
@@ -7957,7 +7978,7 @@
       <c r="E168" s="78" t="n"/>
       <c r="F168" s="78" t="n"/>
     </row>
-    <row r="169" ht="15" customHeight="1">
+    <row r="169" ht="15" customHeight="1" s="183">
       <c r="A169" s="78" t="n"/>
       <c r="B169" s="78" t="n"/>
       <c r="C169" s="78" t="n"/>
@@ -7965,7 +7986,7 @@
       <c r="E169" s="78" t="n"/>
       <c r="F169" s="78" t="n"/>
     </row>
-    <row r="170" ht="15" customHeight="1">
+    <row r="170" ht="15" customHeight="1" s="183">
       <c r="A170" s="78" t="n"/>
       <c r="B170" s="78" t="n"/>
       <c r="C170" s="78" t="n"/>
@@ -7973,7 +7994,7 @@
       <c r="E170" s="78" t="n"/>
       <c r="F170" s="78" t="n"/>
     </row>
-    <row r="171" ht="15" customHeight="1">
+    <row r="171" ht="15" customHeight="1" s="183">
       <c r="A171" s="78" t="n"/>
       <c r="B171" s="78" t="n"/>
       <c r="C171" s="78" t="n"/>
@@ -7981,7 +8002,7 @@
       <c r="E171" s="78" t="n"/>
       <c r="F171" s="78" t="n"/>
     </row>
-    <row r="172" ht="15" customHeight="1">
+    <row r="172" ht="15" customHeight="1" s="183">
       <c r="A172" s="78" t="n"/>
       <c r="B172" s="78" t="n"/>
       <c r="C172" s="78" t="n"/>
@@ -7989,7 +8010,7 @@
       <c r="E172" s="78" t="n"/>
       <c r="F172" s="78" t="n"/>
     </row>
-    <row r="173" ht="15" customHeight="1">
+    <row r="173" ht="15" customHeight="1" s="183">
       <c r="A173" s="78" t="n"/>
       <c r="B173" s="78" t="n"/>
       <c r="C173" s="78" t="n"/>
@@ -7997,7 +8018,7 @@
       <c r="E173" s="78" t="n"/>
       <c r="F173" s="78" t="n"/>
     </row>
-    <row r="174" ht="15" customHeight="1">
+    <row r="174" ht="15" customHeight="1" s="183">
       <c r="A174" s="78" t="n"/>
       <c r="B174" s="78" t="n"/>
       <c r="C174" s="78" t="n"/>
@@ -8005,7 +8026,7 @@
       <c r="E174" s="78" t="n"/>
       <c r="F174" s="78" t="n"/>
     </row>
-    <row r="175" ht="15" customHeight="1">
+    <row r="175" ht="15" customHeight="1" s="183">
       <c r="A175" s="78" t="n"/>
       <c r="B175" s="78" t="n"/>
       <c r="C175" s="78" t="n"/>
@@ -8013,7 +8034,7 @@
       <c r="E175" s="78" t="n"/>
       <c r="F175" s="78" t="n"/>
     </row>
-    <row r="176" ht="15" customHeight="1">
+    <row r="176" ht="15" customHeight="1" s="183">
       <c r="A176" s="78" t="n"/>
       <c r="B176" s="78" t="n"/>
       <c r="C176" s="78" t="n"/>
@@ -8021,7 +8042,7 @@
       <c r="E176" s="78" t="n"/>
       <c r="F176" s="78" t="n"/>
     </row>
-    <row r="177" ht="15" customHeight="1">
+    <row r="177" ht="15" customHeight="1" s="183">
       <c r="A177" s="78" t="n"/>
       <c r="B177" s="78" t="n"/>
       <c r="C177" s="78" t="n"/>
@@ -8029,7 +8050,7 @@
       <c r="E177" s="78" t="n"/>
       <c r="F177" s="78" t="n"/>
     </row>
-    <row r="178" ht="15" customHeight="1">
+    <row r="178" ht="15" customHeight="1" s="183">
       <c r="A178" s="78" t="n"/>
       <c r="B178" s="78" t="n"/>
       <c r="C178" s="78" t="n"/>
@@ -8037,7 +8058,7 @@
       <c r="E178" s="78" t="n"/>
       <c r="F178" s="78" t="n"/>
     </row>
-    <row r="179" ht="15" customHeight="1">
+    <row r="179" ht="15" customHeight="1" s="183">
       <c r="A179" s="78" t="n"/>
       <c r="B179" s="78" t="n"/>
       <c r="C179" s="78" t="n"/>
@@ -8045,7 +8066,7 @@
       <c r="E179" s="78" t="n"/>
       <c r="F179" s="78" t="n"/>
     </row>
-    <row r="180" ht="15" customHeight="1">
+    <row r="180" ht="15" customHeight="1" s="183">
       <c r="A180" s="78" t="n"/>
       <c r="B180" s="78" t="n"/>
       <c r="C180" s="78" t="n"/>
@@ -8053,15 +8074,13 @@
       <c r="E180" s="78" t="n"/>
       <c r="F180" s="78" t="n"/>
     </row>
-    <row r="181"/>
-    <row r="182"/>
-    <row r="183" ht="8.1" customHeight="1"/>
-    <row r="184" ht="6" customHeight="1"/>
-    <row r="185" ht="29.1" customHeight="1">
-      <c r="A185" s="177" t="n"/>
-      <c r="B185" s="177" t="n"/>
-      <c r="C185" s="177" t="n"/>
-      <c r="D185" s="177" t="n"/>
+    <row r="183" ht="8.1" customHeight="1" s="183"/>
+    <row r="184" ht="6" customHeight="1" s="183"/>
+    <row r="185" ht="29.1" customHeight="1" s="183">
+      <c r="A185" s="142" t="n"/>
+      <c r="B185" s="142" t="n"/>
+      <c r="C185" s="142" t="n"/>
+      <c r="D185" s="142" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -8170,76 +8189,15 @@
       <formula>9</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D126:D127">
-    <cfRule type="iconSet" priority="9">
-      <iconSet iconSet="3Arrows" showValue="0">
-        <cfvo type="percent" val="0"/>
-        <cfvo type="num" val="0"/>
-        <cfvo type="num" val="1e-06"/>
-      </iconSet>
+  <conditionalFormatting sqref="D126 D127 D129 D130 D133 D134 D135 D136 D138 D139 D140 D141 D142">
+    <cfRule type="cellIs" priority="36" operator="equal" dxfId="2">
+      <formula>"▲"</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D129">
-    <cfRule type="iconSet" priority="5">
-      <iconSet iconSet="3Arrows" showValue="0" reverse="1">
-        <cfvo type="percent" val="0"/>
-        <cfvo type="num" val="0"/>
-        <cfvo type="num" val="1e-06"/>
-      </iconSet>
+    <cfRule type="cellIs" priority="37" operator="equal" dxfId="0">
+      <formula>"▼"</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D130 D133:D136">
-    <cfRule type="iconSet" priority="8">
-      <iconSet iconSet="3Arrows" showValue="0">
-        <cfvo type="percent" val="0"/>
-        <cfvo type="num" val="0"/>
-        <cfvo type="num" val="1e-06"/>
-      </iconSet>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D138">
-    <cfRule type="iconSet" priority="7">
-      <iconSet iconSet="3Arrows" showValue="0">
-        <cfvo type="percent" val="0"/>
-        <cfvo type="num" val="0"/>
-        <cfvo type="num" val="1e-06"/>
-      </iconSet>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D139">
-    <cfRule type="iconSet" priority="1">
-      <iconSet iconSet="3Arrows" showValue="0" reverse="1">
-        <cfvo type="percent" val="0"/>
-        <cfvo type="num" val="0"/>
-        <cfvo type="num" val="1e-06"/>
-      </iconSet>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D140">
-    <cfRule type="iconSet" priority="6">
-      <iconSet iconSet="3Arrows" showValue="0">
-        <cfvo type="percent" val="0"/>
-        <cfvo type="num" val="0"/>
-        <cfvo type="num" val="1e-06"/>
-      </iconSet>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D141">
-    <cfRule type="iconSet" priority="3">
-      <iconSet iconSet="3Arrows" showValue="0" reverse="1">
-        <cfvo type="percent" val="0"/>
-        <cfvo type="num" val="0"/>
-        <cfvo type="num" val="1e-06"/>
-      </iconSet>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D142">
-    <cfRule type="iconSet" priority="2">
-      <iconSet iconSet="3Arrows" showValue="0" reverse="1">
-        <cfvo type="percent" val="0"/>
-        <cfvo type="num" val="0"/>
-        <cfvo type="num" val="1e-06"/>
-      </iconSet>
+    <cfRule type="cellIs" priority="38" operator="equal" dxfId="37">
+      <formula>"►"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">

--- a/plugins/fs-analysis/skills/analyzing-financial-statements/assets/template.xlsx
+++ b/plugins/fs-analysis/skills/analyzing-financial-statements/assets/template.xlsx
@@ -4483,7 +4483,7 @@
       <c r="B85" s="51" t="n"/>
       <c r="C85" s="2" t="n"/>
       <c r="D85" s="55">
-        <f>"0 € - "&amp;TEXT(D83,"[$-410]#,##0")&amp;" €"</f>
+        <f>"0 € - "&amp;SUBSTITUTE(TEXT(D83,"#,##0"),",",".")&amp;" €"</f>
         <v/>
       </c>
       <c r="E85" s="2" t="n"/>
@@ -6041,19 +6041,19 @@
     </row>
     <row r="24" ht="29.1" customHeight="1" s="183">
       <c r="A24" s="117">
-        <f>IFERROR(TEXT((Input!B8-Input!C8)/Input!C8,"[$-410]+0.00%;[$-410]-0.00%;[$-410]0.00%") &amp; " vs " &amp; TEXT(Input!C8,"[$-410]#,##0"),"n.d.")</f>
+        <f>IFERROR(SUBSTITUTE(TEXT((Input!B8-Input!C8)/Input!C8,"+0.00%;-0.00%;0.00%"),".",",")&amp;" vs "&amp;SUBSTITUTE(TEXT(Input!C8,"#,##0"),",","."),"n.d.")</f>
         <v/>
       </c>
       <c r="B24" s="117">
-        <f>IFERROR(TEXT((Input!B17-Input!C17)/Input!C17,"[$-410]+0.00%;[$-410]-0.00%;[$-410]0.00%") &amp; " vs " &amp; TEXT(Input!C17,"[$-410]#,##0"),"n.d.")</f>
+        <f>IFERROR(SUBSTITUTE(TEXT((Input!B17-Input!C17)/Input!C17,"+0.00%;-0.00%;0.00%"),".",",")&amp;" vs "&amp;SUBSTITUTE(TEXT(Input!C17,"#,##0"),",","."),"n.d.")</f>
         <v/>
       </c>
       <c r="C24" s="117">
-        <f>IFERROR(TEXT(((Input!B17+Input!B14)-(Input!C17+Input!C14))/(Input!C17+Input!C14),"[$-410]+0.00%;[$-410]-0.00%;[$-410]0.00%") &amp; " vs " &amp; TEXT((Input!C17+Input!C14),"[$-410]#,##0"),"n.d.")</f>
+        <f>IFERROR(SUBSTITUTE(TEXT(((Input!B17+Input!B14)-(Input!C17+Input!C14))/(Input!C17+Input!C14),"+0.00%;-0.00%;0.00%"),".",",")&amp;" vs "&amp;SUBSTITUTE(TEXT((Input!C17+Input!C14),"#,##0"),",","."),"n.d.")</f>
         <v/>
       </c>
       <c r="D24" s="117">
-        <f>IFERROR(TEXT((Input!B20-Input!C20)/Input!C20,"[$-410]+0.00%;[$-410]-0.00%;[$-410]0.00%") &amp; " vs " &amp; TEXT(Input!C20,"[$-410]#,##0"),"n.d.")</f>
+        <f>IFERROR(SUBSTITUTE(TEXT((Input!B20-Input!C20)/Input!C20,"+0.00%;-0.00%;0.00%"),".",",")&amp;" vs "&amp;SUBSTITUTE(TEXT(Input!C20,"#,##0"),",","."),"n.d.")</f>
         <v/>
       </c>
       <c r="E24" s="114" t="n"/>
@@ -6113,19 +6113,19 @@
     </row>
     <row r="28" ht="29.1" customHeight="1" s="183">
       <c r="A28" s="117">
-        <f>IFERROR(TEXT((Input!B34-Input!C34)/Input!C34,"[$-410]+0.00%;[$-410]-0.00%;[$-410]0.00%") &amp; " vs " &amp; TEXT(Input!C34,"[$-410]#,##0"),"n.d.")</f>
+        <f>IFERROR(SUBSTITUTE(TEXT((Input!B34-Input!C34)/Input!C34,"+0.00%;-0.00%;0.00%"),".",",")&amp;" vs "&amp;SUBSTITUTE(TEXT(Input!C34,"#,##0"),",","."),"n.d.")</f>
         <v/>
       </c>
       <c r="B28" s="117">
-        <f>IFERROR(TEXT((Input!B40-Input!C40)/Input!C40,"[$-410]+0.00%;[$-410]-0.00%;[$-410]0.00%")&amp;" vs "&amp;TEXT(Input!C40,"[$-410]#,##0"),"n.d.")</f>
+        <f>IFERROR(SUBSTITUTE(TEXT((Input!B40-Input!C40)/Input!C40,"+0.00%;-0.00%;0.00%"),".",",")&amp;" vs "&amp;SUBSTITUTE(TEXT(Input!C40,"#,##0"),",","."),"n.d.")</f>
         <v/>
       </c>
       <c r="C28" s="117">
-        <f>IFERROR(TEXT((Input!B31-Input!C31)/Input!C31,"[$-410]+0.00%;[$-410]-0.00%;[$-410]0.00%") &amp; " vs " &amp; TEXT(Input!C31,"[$-410]#,##0"),"n.d.")</f>
+        <f>IFERROR(SUBSTITUTE(TEXT((Input!B31-Input!C31)/Input!C31,"+0.00%;-0.00%;0.00%"),".",",")&amp;" vs "&amp;SUBSTITUTE(TEXT(Input!C31,"#,##0"),",","."),"n.d.")</f>
         <v/>
       </c>
       <c r="D28" s="117">
-        <f>IFERROR(TEXT((Input!B21-Input!C21)/Input!C21,"[$-410]+0.00%;[$-410]-0.00%;[$-410]0.00%") &amp; " vs " &amp; TEXT(Input!C21,"[$-410]#,##0"),"n.d.")</f>
+        <f>IFERROR(SUBSTITUTE(TEXT((Input!B21-Input!C21)/Input!C21,"+0.00%;-0.00%;0.00%"),".",",")&amp;" vs "&amp;SUBSTITUTE(TEXT(Input!C21,"#,##0"),",","."),"n.d.")</f>
         <v/>
       </c>
       <c r="E28" s="114" t="n"/>
